--- a/stories/arbres/TREE-DIF-002.xlsx
+++ b/stories/arbres/TREE-DIF-002.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sami est sous le pommier, avec papa. Maman arrive bientôt. Une feuille tombe. Des copains jouent. Les corps sont différents. Papa dit : le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Sami est sous le pommier, avec papa. Maman arrive bientôt. Une feuille tombe. Des copains jouent. Les corps sont différents. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,12 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Sami est sous le pommier, avec papa. Maman arrive bientôt. Une feuille tombe. Des copains jouent. Les corps sont différents.
+papa|Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1510,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1539,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sami va vers le bac à sable. Le sable est frais. Un copain a un corps plus rond. Sami dit : on joue. Le corps n'est pas une blague. Ils remplissent un moule. Papa reste tout près. On peut jouer ensemble.</t>
+          <t>Sami va vers le bac à sable. Le sable est frais. Un copain a un corps plus rond. On joue. Le corps n'est pas une blague. Ils remplissent un moule. Papa reste tout près. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1677,13 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sami va vers le bac à sable. Le sable est frais. Un copain a un corps plus rond.
+enfant-m|On joue.
+narrateur|Le corps n'est pas une blague. Ils remplissent un moule. Papa reste tout près. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1864,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le corps est une blague ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2037,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On joue. Le corps n'est pas une blague. Sami respire. Papa est là. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2228,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2395,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Sami pose les cubes dans le sable. Un copain plus rond en ajoute un. On joue. Papa montre le geste, lentement. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2533,6 +2588,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -2697,6 +2757,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le bac à sable. Puis les cubes. Puis rouge. La lumière est claire. Sami range encore un peu, près de papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2924,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3091,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'arrête près de bleu. les cubes est rangé. Une feuille tombe. Sami dit merci à papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3258,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3425,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Sami se souvient de le bac à sable. Et de les cubes. Et de vert. Un linge sèche à l'air. Sami ferme le sac. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3592,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3531,7 +3621,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Sami ouvre le livre près du bac. Un copain plus mince montre une pomme dessinée. On joue. Papa dit : je suis là. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Sami ouvre le livre près du bac. Un copain plus mince montre une pomme dessinée. On joue. Je suis là. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3669,6 +3759,13 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Sami ouvre le livre près du bac. Un copain plus mince montre une pomme dessinée. On joue.
+papa|Je suis là.
+narrateur|Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3857,6 +3954,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -4021,6 +4123,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Avec rouge. Après le livre. Près de le bac à sable. Sami s'arrête. On souffle doucement. Sami montre rouge à papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4183,6 +4290,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4345,6 +4457,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Sami range le livre. bleu reste près de le bac à sable. Ça sent le pain chaud. Maman n'est pas loin. Sami les rejoint. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4507,6 +4624,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4531,7 +4653,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>vert est là. le livre aussi. le bac à sable reste dans le souvenir. Un crochet tient bien le manteau. Sami caresse le doudou. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Vert est là. le livre aussi. le bac à sable reste dans le souvenir. Un crochet tient bien le manteau. Sami caresse le doudou. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4669,6 +4791,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Vert est là. le livre aussi. le bac à sable reste dans le souvenir. Un crochet tient bien le manteau. Sami caresse le doudou. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4831,6 +4958,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4993,6 +5125,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Sami sort la dînette. Un copain d'une autre forme sert le sable, tout doux. On joue. Papa reste tout près. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5181,6 +5318,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -5345,6 +5487,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint rouge. la dînette est rangé. le bac à sable est fini. Une cloche tinte, tout loin. Sami marche près de papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5507,6 +5654,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5669,6 +5821,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Près de bleu. Sami pose la dînette. le bac à sable est derrière. On dit merci. Sami prend la main de papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5831,6 +5988,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5993,6 +6155,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Sami montre vert. Papa a vu le bac à sable. Et la dînette. Un ballon s'immobilise. Sami enfile ses chaussons. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6155,6 +6322,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6179,7 +6351,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Sami va vers le toboggan. Un copain plus mince attend. Sami s'assoit à côté. Le corps n'est pas une blague. On joue ensemble. Ils glissent, chacun son tour. Papa dit : je suis là. On peut jouer ensemble.</t>
+          <t>Sami va vers le toboggan. Un copain plus mince attend. Sami s'assoit à côté. Le corps n'est pas une blague. On joue ensemble. Ils glissent, chacun son tour. Je suis là. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6317,6 +6489,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Sami va vers le toboggan. Un copain plus mince attend. Sami s'assoit à côté. Le corps n'est pas une blague. On joue ensemble. Ils glissent, chacun son tour.
+papa|Je suis là. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6497,6 +6675,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|On joue, sans blague sur le corps ?</t>
         </is>
       </c>
     </row>
@@ -6665,6 +6848,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On joue. Le corps n'est pas une blague. Sami retient le geste. Papa sourit. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6851,6 +7039,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6875,7 +7068,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Sami construit une tour de cubes au pied du toboggan. On joue. Personne ne commente le corps. Papa dit : je suis là. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Sami construit une tour de cubes au pied du toboggan. On joue. Personne ne commente le corps. Je suis là. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7013,6 +7206,13 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Sami construit une tour de cubes au pied du toboggan. On joue. Personne ne commente le corps.
+papa|Je suis là.
+narrateur|Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7201,6 +7401,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -7365,6 +7570,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le toboggan. Puis les cubes. Puis rouge. Un vélo passe au loin. Sami plie un pull. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7527,6 +7737,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7689,6 +7904,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'arrête près de bleu. les cubes est rangé. On range un objet. Sami boit une gorgée d'eau. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7851,6 +8071,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8013,6 +8238,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Sami se souvient de le toboggan. Et de les cubes. Et de vert. Un panier est posé sur le banc. Sami range la tasse. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8175,6 +8405,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8337,6 +8572,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Sami lit une page avant de glisser. Un copain attend. On joue. Le corps n'est pas une blague. Papa reste tout près. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8525,6 +8765,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -8689,6 +8934,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Avec rouge. Après le livre. Près de le toboggan. Sami s'arrête. Il y a des miettes sur la table. Sami range le toboggan dans sa tête, comme un souvenir. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8851,6 +9101,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9013,6 +9268,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Sami range le livre. bleu reste près de le toboggan. Une pomme brille un peu. Sami serre la main de papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9175,6 +9435,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9199,7 +9464,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>vert est là. le livre aussi. le toboggan reste dans le souvenir. On entend un oiseau. Sami raccroche un linge. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Vert est là. le livre aussi. le toboggan reste dans le souvenir. On entend un oiseau. Sami raccroche un linge. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9337,6 +9602,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Vert est là. le livre aussi. le toboggan reste dans le souvenir. On entend un oiseau. Sami raccroche un linge. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9499,6 +9769,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9661,6 +9936,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Sami pose une tasse de dînette sur la marche. On joue. Le corps n'est pas une blague. Papa montre le geste, lentement. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9849,6 +10129,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -10013,6 +10298,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint rouge. la dînette est rangé. le toboggan est fini. On rit un peu. Sami écoute papa encore une fois. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10175,6 +10465,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10337,6 +10632,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Près de bleu. Sami pose la dînette. le toboggan est derrière. La couverture est douce. Sami sourit. Papa sourit aussi. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10499,6 +10799,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10661,6 +10966,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Sami montre vert. Papa a vu le toboggan. Et la dînette. On écoute jusqu'au bout. Sami pose la dînette à sa place. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10823,6 +11133,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10985,6 +11300,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Sami va vers les balançoires. Une feuille tombe du pommier. Un copain d'une autre forme pousse tout doux. Sami joue avec lui. Le corps n'est pas une blague. Papa sourit. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11161,6 +11481,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On fait quoi ? On joue.</t>
         </is>
       </c>
     </row>
@@ -11329,6 +11654,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On joue. Le corps n'est pas une blague. Sami hoche la tête. On continue, avec papa. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11515,6 +11845,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11677,6 +12012,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Sami empile des cubes près des balançoires. Un copain plus rond tient la base. On joue. Papa reste tout près. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11865,6 +12205,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -12029,6 +12374,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi les balançoires. Puis les cubes. Puis rouge. Une tasse cliquette. Sami essuie ses mains. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12191,6 +12541,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12215,7 +12570,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Sami s'arrête près de bleu. les cubes est rangé. Le sol est un peu froid. Sami dit : j'ai appris. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Sami s'arrête près de bleu. les cubes est rangé. Le sol est un peu froid. J'ai appris. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12353,6 +12708,13 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'arrête près de bleu. les cubes est rangé. Le sol est un peu froid.
+enfant-m|J'ai appris.
+narrateur|Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12515,6 +12877,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12677,6 +13044,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Sami se souvient de les balançoires. Et de les cubes. Et de vert. L'eau coule, tout petit bruit. Sami s'assoit près de papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12839,6 +13211,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13001,6 +13378,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Sami montre le livre à un copain plus mince. On joue. Le corps n'est pas une blague. Papa montre le geste, lentement. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13189,6 +13571,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -13353,6 +13740,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Avec rouge. Après le livre. Près de les balançoires. Sami s'arrête. Un galet est encore chaud. Sami répète tout bas le geste. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13515,6 +13907,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13677,6 +14074,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Sami range le livre. bleu reste près de les balançoires. Le savon sent bon. Sami pose sa tête un moment. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13839,6 +14241,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13863,7 +14270,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>vert est là. le livre aussi. les balançoires reste dans le souvenir. Une chaussette est encore sablée. Sami ferme la porte, tout doux. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Vert est là. le livre aussi. les balançoires reste dans le souvenir. Une chaussette est encore sablée. Sami ferme la porte, tout doux. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14001,6 +14408,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Vert est là. le livre aussi. les balançoires reste dans le souvenir. Une chaussette est encore sablée. Sami ferme la porte, tout doux. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14163,6 +14575,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14187,7 +14604,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Sami sert un galet dans la dînette. On joue. Le corps n'est pas une blague. Papa dit : je suis là. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Sami sert un galet dans la dînette. On joue. Le corps n'est pas une blague. Je suis là. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14325,6 +14742,13 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Sami sert un galet dans la dînette. On joue. Le corps n'est pas une blague.
+papa|Je suis là.
+narrateur|Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14513,6 +14937,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -14677,6 +15106,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint rouge. la dînette est rangé. les balançoires est fini. On attend son tour. Sami souffle, puis sourit à papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14839,6 +15273,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15001,6 +15440,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Près de bleu. Sami pose la dînette. les balançoires est derrière. Le vent est doux. Sami tend bleu à maman. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15163,6 +15607,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15325,6 +15774,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Sami montre vert. Papa a vu les balançoires. Et la dînette. Les chaussures font toc toc. Sami chuchote : c'est fini. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15487,6 +15941,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15505,7 +15964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15578,6 +16037,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-002.xlsx
+++ b/stories/arbres/TREE-DIF-002.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1324,6 +1329,7 @@
 papa|Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1515,6 +1521,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1684,6 +1691,7 @@
 narrateur|Le corps n'est pas une blague. Ils remplissent un moule. Papa reste tout près. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1871,6 +1879,7 @@
           <t>narrateur|Le corps est une blague ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2042,6 +2051,7 @@
           <t>narrateur|Oui. On joue. Le corps n'est pas une blague. Sami respire. Papa est là. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2233,6 +2243,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2400,6 +2411,7 @@
           <t>narrateur|Sami pose les cubes dans le sable. Un copain plus rond en ajoute un. On joue. Papa montre le geste, lentement. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2595,6 +2607,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2762,6 +2775,7 @@
           <t>narrateur|Sami a choisi le bac à sable. Puis les cubes. Puis rouge. La lumière est claire. Sami range encore un peu, près de papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2929,6 +2943,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3096,6 +3111,7 @@
           <t>narrateur|Sami s'arrête près de bleu. les cubes est rangé. Une feuille tombe. Sami dit merci à papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3263,6 +3279,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3430,6 +3447,7 @@
           <t>narrateur|Sami se souvient de le bac à sable. Et de les cubes. Et de vert. Un linge sèche à l'air. Sami ferme le sac. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3597,6 +3615,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3766,6 +3785,7 @@
 narrateur|Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3961,6 +3981,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4128,6 +4149,7 @@
           <t>narrateur|Avec rouge. Après le livre. Près de le bac à sable. Sami s'arrête. On souffle doucement. Sami montre rouge à papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4295,6 +4317,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4462,6 +4485,7 @@
           <t>narrateur|Sami range le livre. bleu reste près de le bac à sable. Ça sent le pain chaud. Maman n'est pas loin. Sami les rejoint. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4629,6 +4653,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4796,6 +4821,7 @@
           <t>narrateur|Vert est là. le livre aussi. le bac à sable reste dans le souvenir. Un crochet tient bien le manteau. Sami caresse le doudou. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4963,6 +4989,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5130,6 +5157,7 @@
           <t>narrateur|Sami sort la dînette. Un copain d'une autre forme sert le sable, tout doux. On joue. Papa reste tout près. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5325,6 +5353,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5492,6 +5521,7 @@
           <t>narrateur|Sami rejoint rouge. la dînette est rangé. le bac à sable est fini. Une cloche tinte, tout loin. Sami marche près de papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5659,6 +5689,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5826,6 +5857,7 @@
           <t>narrateur|Près de bleu. Sami pose la dînette. le bac à sable est derrière. On dit merci. Sami prend la main de papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5993,6 +6025,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6160,6 +6193,7 @@
           <t>narrateur|Sami montre vert. Papa a vu le bac à sable. Et la dînette. Un ballon s'immobilise. Sami enfile ses chaussons. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6327,6 +6361,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6495,6 +6530,7 @@
 papa|Je suis là. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6682,6 +6718,7 @@
           <t>narrateur|On joue, sans blague sur le corps ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6853,6 +6890,7 @@
           <t>narrateur|Oui. On joue. Le corps n'est pas une blague. Sami retient le geste. Papa sourit. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7044,6 +7082,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7213,6 +7252,7 @@
 narrateur|Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7408,6 +7448,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7575,6 +7616,7 @@
           <t>narrateur|Sami a choisi le toboggan. Puis les cubes. Puis rouge. Un vélo passe au loin. Sami plie un pull. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7742,6 +7784,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7909,6 +7952,7 @@
           <t>narrateur|Sami s'arrête près de bleu. les cubes est rangé. On range un objet. Sami boit une gorgée d'eau. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8076,6 +8120,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8243,6 +8288,7 @@
           <t>narrateur|Sami se souvient de le toboggan. Et de les cubes. Et de vert. Un panier est posé sur le banc. Sami range la tasse. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8410,6 +8456,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8577,6 +8624,7 @@
           <t>narrateur|Sami lit une page avant de glisser. Un copain attend. On joue. Le corps n'est pas une blague. Papa reste tout près. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8772,6 +8820,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8939,6 +8988,7 @@
           <t>narrateur|Avec rouge. Après le livre. Près de le toboggan. Sami s'arrête. Il y a des miettes sur la table. Sami range le toboggan dans sa tête, comme un souvenir. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9106,6 +9156,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9273,6 +9324,7 @@
           <t>narrateur|Sami range le livre. bleu reste près de le toboggan. Une pomme brille un peu. Sami serre la main de papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9440,6 +9492,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9607,6 +9660,7 @@
           <t>narrateur|Vert est là. le livre aussi. le toboggan reste dans le souvenir. On entend un oiseau. Sami raccroche un linge. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9774,6 +9828,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9941,6 +9996,7 @@
           <t>narrateur|Sami pose une tasse de dînette sur la marche. On joue. Le corps n'est pas une blague. Papa montre le geste, lentement. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10136,6 +10192,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10303,6 +10360,7 @@
           <t>narrateur|Sami rejoint rouge. la dînette est rangé. le toboggan est fini. On rit un peu. Sami écoute papa encore une fois. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10470,6 +10528,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10637,6 +10696,7 @@
           <t>narrateur|Près de bleu. Sami pose la dînette. le toboggan est derrière. La couverture est douce. Sami sourit. Papa sourit aussi. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10804,6 +10864,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10971,6 +11032,7 @@
           <t>narrateur|Sami montre vert. Papa a vu le toboggan. Et la dînette. On écoute jusqu'au bout. Sami pose la dînette à sa place. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11138,6 +11200,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11305,6 +11368,7 @@
           <t>narrateur|Sami va vers les balançoires. Une feuille tombe du pommier. Un copain d'une autre forme pousse tout doux. Sami joue avec lui. Le corps n'est pas une blague. Papa sourit. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11488,6 +11552,7 @@
           <t>narrateur|On fait quoi ? On joue.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11659,6 +11724,7 @@
           <t>narrateur|Oui. On joue. Le corps n'est pas une blague. Sami hoche la tête. On continue, avec papa. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11850,6 +11916,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12017,6 +12084,7 @@
           <t>narrateur|Sami empile des cubes près des balançoires. Un copain plus rond tient la base. On joue. Papa reste tout près. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12212,6 +12280,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12379,6 +12448,7 @@
           <t>narrateur|Sami a choisi les balançoires. Puis les cubes. Puis rouge. Une tasse cliquette. Sami essuie ses mains. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12546,6 +12616,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12715,6 +12786,7 @@
 narrateur|Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12882,6 +12954,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13049,6 +13122,7 @@
           <t>narrateur|Sami se souvient de les balançoires. Et de les cubes. Et de vert. L'eau coule, tout petit bruit. Sami s'assoit près de papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13216,6 +13290,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13383,6 +13458,7 @@
           <t>narrateur|Sami montre le livre à un copain plus mince. On joue. Le corps n'est pas une blague. Papa montre le geste, lentement. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13578,6 +13654,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13745,6 +13822,7 @@
           <t>narrateur|Avec rouge. Après le livre. Près de les balançoires. Sami s'arrête. Un galet est encore chaud. Sami répète tout bas le geste. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13912,6 +13990,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14079,6 +14158,7 @@
           <t>narrateur|Sami range le livre. bleu reste près de les balançoires. Le savon sent bon. Sami pose sa tête un moment. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14246,6 +14326,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14413,6 +14494,7 @@
           <t>narrateur|Vert est là. le livre aussi. les balançoires reste dans le souvenir. Une chaussette est encore sablée. Sami ferme la porte, tout doux. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14580,6 +14662,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14749,6 +14832,7 @@
 narrateur|Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14944,6 +15028,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15111,6 +15196,7 @@
           <t>narrateur|Sami rejoint rouge. la dînette est rangé. les balançoires est fini. On attend son tour. Sami souffle, puis sourit à papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15278,6 +15364,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15445,6 +15532,7 @@
           <t>narrateur|Près de bleu. Sami pose la dînette. les balançoires est derrière. Le vent est doux. Sami tend bleu à maman. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15612,6 +15700,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15779,6 +15868,7 @@
           <t>narrateur|Sami montre vert. Papa a vu les balançoires. Et la dînette. Les chaussures font toc toc. Sami chuchote : c'est fini. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15946,6 +16036,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15964,7 +16055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16044,6 +16135,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16058,7 +16163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16245,6 +16350,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-DIF-002.xlsx
+++ b/stories/arbres/TREE-DIF-002.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Plus rond ou plus mince — sous le pommier</t>
+          <t>Le pull bleu et les deux pommes</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sous le pommier, deux pommes n'ont pas la même forme. Amir et Nino jouent. Le corps n'est pas une blague.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sami est sous le pommier, avec papa. Maman arrive bientôt. Une feuille tombe. Des copains jouent. Les corps sont différents. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Le soleil perce les feuilles du pommier. Des ronds de lumière dansent sur l'herbe. Une pomme verte a une joue rouge. Une autre est toute ronde, toute jaune. Un pull bleu pend à la branche basse. Il sent encore le savon. Papa range deux pommes dans le panier. Elles n'ont pas la même forme. Maman essuie une feuille sur la nappe. Ça sent l'herbe coupée. Tu sens, Amir ? Ça sent la pomme. Elle est froide. Le pull sèche, tout doux. En ce moment, Amir pose sa main sur l'écorce. L'écorce est rêche, un peu chaude. Nino arrive près du panier. Ses chaussettes sont jaunes. Nino a un corps plus rond. Amir a des bras plus minces. On joue ensemble. Le corps n'est pas une blague. On joue. On joue. L'amitié ne dépend pas de la forme. On peut jouer. Une coccinelle marche sur une feuille, tout lentement. Le pull bleu bouge un peu, sur la branche.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,11 +1337,41 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Sami est sous le pommier, avec papa. Maman arrive bientôt. Une feuille tombe. Des copains jouent. Les corps sont différents.
-papa|Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le soleil perce les feuilles du pommier.
+narrateur|Des ronds de lumière dansent sur l'herbe.
+narrateur|Une pomme verte a une joue rouge.
+narrateur|Une autre est toute ronde, toute jaune.
+narrateur|Un pull bleu pend à la branche basse.
+narrateur|Il sent encore le savon.
+narrateur|Papa range deux pommes dans le panier.
+narrateur|Elles n'ont pas la même forme.
+narrateur|Maman essuie une feuille sur la nappe.
+narrateur|Ça sent l'herbe coupée.
+papa|Tu sens, Amir ?
+papa|Ça sent la pomme.
+enfant-m|Elle est froide.
+maman|Le pull sèche, tout doux.
+narrateur|En ce moment, Amir pose sa main sur l'écorce.
+narrateur|L'écorce est rêche, un peu chaude.
+narrateur|Nino arrive près du panier.
+narrateur|Ses chaussettes sont jaunes.
+narrateur|Nino a un corps plus rond.
+narrateur|Amir a des bras plus minces.
+papa|On joue ensemble.
+papa|Le corps n'est pas une blague.
+enfant-m|On joue.
+copain|On joue.
+maman|L'amitié ne dépend pas de la forme.
+maman|On peut jouer.
+narrateur|Une coccinelle marche sur une feuille, tout lentement.
+narrateur|Le pull bleu bouge un peu, sur la branche.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>oiseau,feuille</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1354,7 +1396,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>Trois coins du jardin attendent. Le bac à sable, le toboggan, ou les balançoires ? On joue ensemble.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1518,7 +1560,9 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>narrateur|Trois coins du jardin attendent.
+papa|Le bac à sable, le toboggan, ou les balançoires ?
+maman|On joue ensemble.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1546,7 +1590,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sami va vers le bac à sable. Le sable est frais. Un copain a un corps plus rond. On joue. Le corps n'est pas une blague. Ils remplissent un moule. Papa reste tout près. On peut jouer ensemble.</t>
+          <t>Amir s'agenouille près du bac à sable. Le sable est frais, un peu rêche. Un grain colle à son genou. Nino s'assoit à côté, tout calme. Nino a un corps plus rond. Amir a des bras plus minces. On joue ensemble. Le corps n'est pas une blague. On joue. On joue. Ils remplissent un moule, chacun. Le sable sent la terre mouillée. Bravo, Amir. Tu as invité Nino. L'amitié ne dépend pas de la forme. Un gâteau de sable tient, tout doux. Il est beau. Le mien aussi. Vous jouez. C'est ça. Une fourmi passe au bord du bac.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1686,12 +1730,34 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sami va vers le bac à sable. Le sable est frais. Un copain a un corps plus rond.
+          <t>narrateur|Amir s'agenouille près du bac à sable.
+narrateur|Le sable est frais, un peu rêche.
+narrateur|Un grain colle à son genou.
+narrateur|Nino s'assoit à côté, tout calme.
+narrateur|Nino a un corps plus rond.
+narrateur|Amir a des bras plus minces.
+papa|On joue ensemble.
+papa|Le corps n'est pas une blague.
 enfant-m|On joue.
-narrateur|Le corps n'est pas une blague. Ils remplissent un moule. Papa reste tout près. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+copain|On joue.
+narrateur|Ils remplissent un moule, chacun.
+narrateur|Le sable sent la terre mouillée.
+maman|Bravo, Amir.
+maman|Tu as invité Nino.
+papa|L'amitié ne dépend pas de la forme.
+narrateur|Un gâteau de sable tient, tout doux.
+enfant-m|Il est beau.
+copain|Le mien aussi.
+maman|Vous jouez.
+maman|C'est ça.
+narrateur|Une fourmi passe au bord du bac.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>sable</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1716,7 +1782,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le corps est une blague ?</t>
+          <t>Nino a un corps plus rond. On joue ensemble ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1876,7 +1942,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le corps est une blague ?</t>
+          <t>narrateur|Nino a un corps plus rond.
+papa|On joue ensemble ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1904,7 +1971,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. On joue. Le corps n'est pas une blague. Sami respire. Papa est là. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Oui. On joue. Le corps n'est pas une blague. Amir souffle un peu. Un grain de sable reste sur son genou. On joue. Bravo, Amir. Tu as fait du bon travail. Le moule garde encore la forme du gâteau.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2048,7 +2115,15 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On joue. Le corps n'est pas une blague. Sami respire. Papa est là. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+          <t>papa|Oui.
+papa|On joue.
+papa|Le corps n'est pas une blague.
+narrateur|Amir souffle un peu.
+narrateur|Un grain de sable reste sur son genou.
+enfant-m|On joue.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|Le moule garde encore la forme du gâteau.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2076,7 +2151,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Trois jeux attendent, tout proches. Les cubes, le livre, ou la dînette ? On joue. Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2240,7 +2315,10 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Trois jeux attendent, tout proches.
+maman|Les cubes, le livre, ou la dînette ?
+papa|On joue.
+papa|Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2268,7 +2346,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Sami pose les cubes dans le sable. Un copain plus rond en ajoute un. On joue. Papa montre le geste, lentement. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Amir prend les cubes en bois. Un cube rouge sent le pin. Un cube vert fait clic. Nino pose un cube, tout droit. Vous construisez ensemble ? Oui. Oui. Le corps n'est pas une blague. On joue. Nino tient la base. Amir pose le petit cube. La tour tient. Elle est haute. Encore un. Bravo. Vous jouez ensemble. Un cube attrape un grain de sable, tout fin. On est encore près de le bac à sable. On joue ensemble. Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2408,10 +2486,33 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Sami pose les cubes dans le sable. Un copain plus rond en ajoute un. On joue. Papa montre le geste, lentement. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+          <t>narrateur|Amir prend les cubes en bois.
+narrateur|Un cube rouge sent le pin.
+narrateur|Un cube vert fait clic.
+narrateur|Nino pose un cube, tout droit.
+papa|Vous construisez ensemble ?
+enfant-m|Oui.
+copain|Oui.
+maman|Le corps n'est pas une blague.
+maman|On joue.
+papa|Nino tient la base.
+papa|Amir pose le petit cube.
+narrateur|La tour tient.
+enfant-m|Elle est haute.
+copain|Encore un.
+maman|Bravo.
+maman|Vous jouez ensemble.
+narrateur|Un cube attrape un grain de sable, tout fin.
+narrateur|On est encore près de le bac à sable.
+papa|On joue ensemble.
+maman|Le corps n'est pas une blague.</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>cubes</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2436,7 +2537,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>Quelle couleur, maintenant ? Rouge, bleu, ou vert ? On joue encore ensemble.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2604,7 +2705,9 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|Quelle couleur, maintenant ?
+papa|Rouge, bleu, ou vert ?
+maman|On joue encore ensemble.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2632,7 +2735,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi le bac à sable. Puis les cubes. Puis rouge. La lumière est claire. Sami range encore un peu, près de papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Le rouge arrive, tout vif. Une pomme rouge brille dans l'herbe. Un seau rouge attend, tout près. Tu vois le rouge, Amir ? Oui, papa. Amir a encore les cubes, près de le bac à sable. Nino est encore là, tout près. Un cube rouge a du sable sur une arête. On joue encore ? Oui. Oui. Le corps n'est pas une blague. On joue ensemble. On ne commente pas le corps. Merci, Nino. Merci, Amir. Bravo. C'est du bon travail. Amir range les cubes, tout doux. Tu as fini de ranger un peu ? Oui, papa.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2772,10 +2875,34 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi le bac à sable. Puis les cubes. Puis rouge. La lumière est claire. Sami range encore un peu, près de papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr"/>
+          <t>narrateur|Le rouge arrive, tout vif.
+narrateur|Une pomme rouge brille dans l'herbe.
+narrateur|Un seau rouge attend, tout près.
+papa|Tu vois le rouge, Amir ?
+enfant-m|Oui, papa.
+narrateur|Amir a encore les cubes, près de le bac à sable.
+narrateur|Nino est encore là, tout près.
+narrateur|Un cube rouge a du sable sur une arête.
+papa|On joue encore ?
+enfant-m|Oui.
+copain|Oui.
+maman|Le corps n'est pas une blague.
+maman|On joue ensemble.
+papa|On ne commente pas le corps.
+enfant-m|Merci, Nino.
+copain|Merci, Amir.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Amir range les cubes, tout doux.
+papa|Tu as fini de ranger un peu ?
+enfant-m|Oui, papa.</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2800,7 +2927,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Amir a vécu le rouge, près de le bac à sable. Il a joué avec les cubes, et avec Nino. La pomme rouge reste dans le panier, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2940,7 +3067,15 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué.
+copain|On a joué.
+papa|Le corps n'est pas une blague.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|Amir a vécu le rouge, près de le bac à sable.
+narrateur|Il a joué avec les cubes, et avec Nino.
+narrateur|La pomme rouge reste dans le panier, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2968,7 +3103,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Sami s'arrête près de bleu. les cubes est rangé. Une feuille tombe. Sami dit merci à papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Le bleu s'installe, tout calme. Le ciel est bleu, tout haut. Une pelle bleue repose dans l'herbe. Tu vois le bleu, Amir ? Oui, maman. Amir a encore les cubes, près de le bac à sable. Nino est encore là, tout près. Un cube bleu sèche au soleil, près du bac. On joue encore ? Oui. Oui. Le corps n'est pas une blague. On joue ensemble. On ne commente pas le corps. Merci, Nino. Merci, Amir. Bravo. C'est du bon travail. Amir range les cubes, tout doux. Tu as fini de ranger un peu ? Oui, papa.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3108,7 +3243,27 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Sami s'arrête près de bleu. les cubes est rangé. Une feuille tombe. Sami dit merci à papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>narrateur|Le bleu s'installe, tout calme.
+narrateur|Le ciel est bleu, tout haut.
+narrateur|Une pelle bleue repose dans l'herbe.
+maman|Tu vois le bleu, Amir ?
+enfant-m|Oui, maman.
+narrateur|Amir a encore les cubes, près de le bac à sable.
+narrateur|Nino est encore là, tout près.
+narrateur|Un cube bleu sèche au soleil, près du bac.
+papa|On joue encore ?
+enfant-m|Oui.
+copain|Oui.
+maman|Le corps n'est pas une blague.
+maman|On joue ensemble.
+papa|On ne commente pas le corps.
+enfant-m|Merci, Nino.
+copain|Merci, Amir.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Amir range les cubes, tout doux.
+papa|Tu as fini de ranger un peu ?
+enfant-m|Oui, papa.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3136,7 +3291,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Amir a vécu le bleu, près de le bac à sable. Il a joué avec les cubes, et avec Nino. La pelle bleue sèche dans l'herbe, tout sage. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3276,7 +3431,15 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué.
+copain|On a joué.
+papa|Le corps n'est pas une blague.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|Amir a vécu le bleu, près de le bac à sable.
+narrateur|Il a joué avec les cubes, et avec Nino.
+narrateur|La pelle bleue sèche dans l'herbe, tout sage.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3304,7 +3467,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Sami se souvient de le bac à sable. Et de les cubes. Et de vert. Un linge sèche à l'air. Sami ferme le sac. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Le vert est partout, tout doux. L'herbe est verte, encore un peu mouillée. Une feuille verte colle à la chaussette. Tu vois le vert, Amir ? Oui, papa. Amir a encore les cubes, près de le bac à sable. Nino est encore là, tout près. Un cube vert garde une tache d'herbe. On joue encore ? Oui. Oui. Le corps n'est pas une blague. On joue ensemble. On ne commente pas le corps. Merci, Nino. Merci, Amir. Bravo. C'est du bon travail. Amir range les cubes, tout doux. Tu as fini de ranger un peu ? Oui, papa.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3444,10 +3607,34 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Sami se souvient de le bac à sable. Et de les cubes. Et de vert. Un linge sèche à l'air. Sami ferme le sac. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr"/>
+          <t>narrateur|Le vert est partout, tout doux.
+narrateur|L'herbe est verte, encore un peu mouillée.
+narrateur|Une feuille verte colle à la chaussette.
+papa|Tu vois le vert, Amir ?
+enfant-m|Oui, papa.
+narrateur|Amir a encore les cubes, près de le bac à sable.
+narrateur|Nino est encore là, tout près.
+narrateur|Un cube vert garde une tache d'herbe.
+papa|On joue encore ?
+enfant-m|Oui.
+copain|Oui.
+maman|Le corps n'est pas une blague.
+maman|On joue ensemble.
+papa|On ne commente pas le corps.
+enfant-m|Merci, Nino.
+copain|Merci, Amir.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Amir range les cubes, tout doux.
+papa|Tu as fini de ranger un peu ?
+enfant-m|Oui, papa.</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>feuille</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3472,7 +3659,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Amir a vécu le vert, près de le bac à sable. Il a joué avec les cubes, et avec Nino. La feuille verte ne bouge plus, sur le pull. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3612,7 +3799,15 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué.
+copain|On a joué.
+papa|Le corps n'est pas une blague.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|Amir a vécu le vert, près de le bac à sable.
+narrateur|Il a joué avec les cubes, et avec Nino.
+narrateur|La feuille verte ne bouge plus, sur le pull.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3640,7 +3835,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Sami ouvre le livre près du bac. Un copain plus mince montre une pomme dessinée. On joue. Je suis là. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Amir ouvre le livre. La page sent le papier, un peu sec. Une pomme est dessinée, toute rouge. Nino montre la pomme du doigt. On lit ensemble ? Oui. La pomme. On joue. Le corps n'est pas une blague. L'amitié ne dépend pas de la forme. Amir tourne la page, tout doux. Une feuille collée sert de marque-page. Encore. Bravo, Amir. Tu as partagé le livre. Le livre a une tache de sable, toute petite. On est encore près de le bac à sable. On joue ensemble. Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3780,12 +3975,32 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Sami ouvre le livre près du bac. Un copain plus mince montre une pomme dessinée. On joue.
-papa|Je suis là.
-narrateur|Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr"/>
+          <t>narrateur|Amir ouvre le livre.
+narrateur|La page sent le papier, un peu sec.
+narrateur|Une pomme est dessinée, toute rouge.
+narrateur|Nino montre la pomme du doigt.
+papa|On lit ensemble ?
+enfant-m|Oui.
+copain|La pomme.
+maman|On joue.
+maman|Le corps n'est pas une blague.
+papa|L'amitié ne dépend pas de la forme.
+narrateur|Amir tourne la page, tout doux.
+narrateur|Une feuille collée sert de marque-page.
+enfant-m|Encore.
+maman|Bravo, Amir.
+maman|Tu as partagé le livre.
+narrateur|Le livre a une tache de sable, toute petite.
+narrateur|On est encore près de le bac à sable.
+papa|On joue ensemble.
+maman|Le corps n'est pas une blague.</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3810,7 +4025,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>Quelle couleur, maintenant ? Rouge, bleu, ou vert ? On joue encore ensemble.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3978,7 +4193,9 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|Quelle couleur, maintenant ?
+papa|Rouge, bleu, ou vert ?
+maman|On joue encore ensemble.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -4006,7 +4223,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Avec rouge. Après le livre. Près de le bac à sable. Sami s'arrête. On souffle doucement. Sami montre rouge à papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Le rouge arrive, tout vif. Une pomme rouge brille dans l'herbe. Un seau rouge attend, tout près. Tu vois le rouge, Amir ? Oui, papa. Amir a encore le livre, près de le bac à sable. Nino est encore là, tout près. La pomme du livre est rouge, comme celle de l'herbe. On joue encore ? Oui. Oui. Le corps n'est pas une blague. On joue ensemble. On ne commente pas le corps. Merci, Nino. Merci, Amir. Bravo. C'est du bon travail. Amir range le livre, tout doux. Tu as fini de ranger un peu ? Oui, papa.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4146,10 +4363,34 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Avec rouge. Après le livre. Près de le bac à sable. Sami s'arrête. On souffle doucement. Sami montre rouge à papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr"/>
+          <t>narrateur|Le rouge arrive, tout vif.
+narrateur|Une pomme rouge brille dans l'herbe.
+narrateur|Un seau rouge attend, tout près.
+papa|Tu vois le rouge, Amir ?
+enfant-m|Oui, papa.
+narrateur|Amir a encore le livre, près de le bac à sable.
+narrateur|Nino est encore là, tout près.
+narrateur|La pomme du livre est rouge, comme celle de l'herbe.
+papa|On joue encore ?
+enfant-m|Oui.
+copain|Oui.
+maman|Le corps n'est pas une blague.
+maman|On joue ensemble.
+papa|On ne commente pas le corps.
+enfant-m|Merci, Nino.
+copain|Merci, Amir.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Amir range le livre, tout doux.
+papa|Tu as fini de ranger un peu ?
+enfant-m|Oui, papa.</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4174,7 +4415,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Amir a vécu le rouge, près de le bac à sable. Il a joué avec le livre, et avec Nino. La pomme rouge reste dans le panier, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4314,7 +4555,15 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué.
+copain|On a joué.
+papa|Le corps n'est pas une blague.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|Amir a vécu le rouge, près de le bac à sable.
+narrateur|Il a joué avec le livre, et avec Nino.
+narrateur|La pomme rouge reste dans le panier, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4342,7 +4591,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Sami range le livre. bleu reste près de le bac à sable. Ça sent le pain chaud. Maman n'est pas loin. Sami les rejoint. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Le bleu s'installe, tout calme. Le ciel est bleu, tout haut. Une pelle bleue repose dans l'herbe. Tu vois le bleu, Amir ? Oui, maman. Amir a encore le livre, près de le bac à sable. Nino est encore là, tout près. Une tache bleue du ciel passe sur la page. On joue encore ? Oui. Oui. Le corps n'est pas une blague. On joue ensemble. On ne commente pas le corps. Merci, Nino. Merci, Amir. Bravo. C'est du bon travail. Amir range le livre, tout doux. Tu as fini de ranger un peu ? Oui, papa.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4482,7 +4731,27 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Sami range le livre. bleu reste près de le bac à sable. Ça sent le pain chaud. Maman n'est pas loin. Sami les rejoint. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>narrateur|Le bleu s'installe, tout calme.
+narrateur|Le ciel est bleu, tout haut.
+narrateur|Une pelle bleue repose dans l'herbe.
+maman|Tu vois le bleu, Amir ?
+enfant-m|Oui, maman.
+narrateur|Amir a encore le livre, près de le bac à sable.
+narrateur|Nino est encore là, tout près.
+narrateur|Une tache bleue du ciel passe sur la page.
+papa|On joue encore ?
+enfant-m|Oui.
+copain|Oui.
+maman|Le corps n'est pas une blague.
+maman|On joue ensemble.
+papa|On ne commente pas le corps.
+enfant-m|Merci, Nino.
+copain|Merci, Amir.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Amir range le livre, tout doux.
+papa|Tu as fini de ranger un peu ?
+enfant-m|Oui, papa.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4510,7 +4779,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Amir a vécu le bleu, près de le bac à sable. Il a joué avec le livre, et avec Nino. La pelle bleue sèche dans l'herbe, tout sage. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4650,7 +4919,15 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué.
+copain|On a joué.
+papa|Le corps n'est pas une blague.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|Amir a vécu le bleu, près de le bac à sable.
+narrateur|Il a joué avec le livre, et avec Nino.
+narrateur|La pelle bleue sèche dans l'herbe, tout sage.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4678,7 +4955,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Vert est là. le livre aussi. le bac à sable reste dans le souvenir. Un crochet tient bien le manteau. Sami caresse le doudou. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Le vert est partout, tout doux. L'herbe est verte, encore un peu mouillée. Une feuille verte colle à la chaussette. Tu vois le vert, Amir ? Oui, papa. Amir a encore le livre, près de le bac à sable. Nino est encore là, tout près. Une vraie feuille verte marque encore la page. On joue encore ? Oui. Oui. Le corps n'est pas une blague. On joue ensemble. On ne commente pas le corps. Merci, Nino. Merci, Amir. Bravo. C'est du bon travail. Amir range le livre, tout doux. Tu as fini de ranger un peu ? Oui, papa.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4818,10 +5095,34 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Vert est là. le livre aussi. le bac à sable reste dans le souvenir. Un crochet tient bien le manteau. Sami caresse le doudou. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr"/>
+          <t>narrateur|Le vert est partout, tout doux.
+narrateur|L'herbe est verte, encore un peu mouillée.
+narrateur|Une feuille verte colle à la chaussette.
+papa|Tu vois le vert, Amir ?
+enfant-m|Oui, papa.
+narrateur|Amir a encore le livre, près de le bac à sable.
+narrateur|Nino est encore là, tout près.
+narrateur|Une vraie feuille verte marque encore la page.
+papa|On joue encore ?
+enfant-m|Oui.
+copain|Oui.
+maman|Le corps n'est pas une blague.
+maman|On joue ensemble.
+papa|On ne commente pas le corps.
+enfant-m|Merci, Nino.
+copain|Merci, Amir.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Amir range le livre, tout doux.
+papa|Tu as fini de ranger un peu ?
+enfant-m|Oui, papa.</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>feuille</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4846,7 +5147,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Amir a vécu le vert, près de le bac à sable. Il a joué avec le livre, et avec Nino. La feuille verte ne bouge plus, sur le pull. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4986,7 +5287,15 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué.
+copain|On a joué.
+papa|Le corps n'est pas une blague.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|Amir a vécu le vert, près de le bac à sable.
+narrateur|Il a joué avec le livre, et avec Nino.
+narrateur|La feuille verte ne bouge plus, sur le pull.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5014,7 +5323,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Sami sort la dînette. Un copain d'une autre forme sert le sable, tout doux. On joue. Papa reste tout près. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Amir sort la dînette. Une petite assiette sonne, tout creux. Une cuillère miniature est encore tiède. Nino sert le sable, tout doux. Tu sers Nino ? Oui. Merci. On joue ensemble. Le corps n'est pas une blague. Ils posent deux tasses, côte à côte. C'est du goûter. Bravo. Vous avez partagé. On ne commente pas le corps. Une goutte perle au bord de l'assiette. La petite casserole laisse un rond dans le sable. On est encore près de le bac à sable. On joue ensemble. Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5154,10 +5463,32 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Sami sort la dînette. Un copain d'une autre forme sert le sable, tout doux. On joue. Papa reste tout près. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr"/>
+          <t>narrateur|Amir sort la dînette.
+narrateur|Une petite assiette sonne, tout creux.
+narrateur|Une cuillère miniature est encore tiède.
+narrateur|Nino sert le sable, tout doux.
+maman|Tu sers Nino ?
+enfant-m|Oui.
+copain|Merci.
+papa|On joue ensemble.
+papa|Le corps n'est pas une blague.
+narrateur|Ils posent deux tasses, côte à côte.
+enfant-m|C'est du goûter.
+maman|Bravo.
+maman|Vous avez partagé.
+papa|On ne commente pas le corps.
+narrateur|Une goutte perle au bord de l'assiette.
+narrateur|La petite casserole laisse un rond dans le sable.
+narrateur|On est encore près de le bac à sable.
+papa|On joue ensemble.
+maman|Le corps n'est pas une blague.</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>assiette</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5182,7 +5513,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>Quelle couleur, maintenant ? Rouge, bleu, ou vert ? On joue encore ensemble.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5350,7 +5681,9 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|Quelle couleur, maintenant ?
+papa|Rouge, bleu, ou vert ?
+maman|On joue encore ensemble.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5378,7 +5711,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint rouge. la dînette est rangé. le bac à sable est fini. Une cloche tinte, tout loin. Sami marche près de papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Le rouge arrive, tout vif. Une pomme rouge brille dans l'herbe. Un seau rouge attend, tout près. Tu vois le rouge, Amir ? Oui, papa. Amir a encore la dînette, près de le bac à sable. Nino est encore là, tout près. La petite assiette a un rond de sable rouge. On joue encore ? Oui. Oui. Le corps n'est pas une blague. On joue ensemble. On ne commente pas le corps. Merci, Nino. Merci, Amir. Bravo. C'est du bon travail. Amir range la dînette, tout doux. Tu as fini de ranger un peu ? Oui, papa.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5518,10 +5851,34 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint rouge. la dînette est rangé. le bac à sable est fini. Une cloche tinte, tout loin. Sami marche près de papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr"/>
+          <t>narrateur|Le rouge arrive, tout vif.
+narrateur|Une pomme rouge brille dans l'herbe.
+narrateur|Un seau rouge attend, tout près.
+papa|Tu vois le rouge, Amir ?
+enfant-m|Oui, papa.
+narrateur|Amir a encore la dînette, près de le bac à sable.
+narrateur|Nino est encore là, tout près.
+narrateur|La petite assiette a un rond de sable rouge.
+papa|On joue encore ?
+enfant-m|Oui.
+copain|Oui.
+maman|Le corps n'est pas une blague.
+maman|On joue ensemble.
+papa|On ne commente pas le corps.
+enfant-m|Merci, Nino.
+copain|Merci, Amir.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Amir range la dînette, tout doux.
+papa|Tu as fini de ranger un peu ?
+enfant-m|Oui, papa.</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5546,7 +5903,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Amir a vécu le rouge, près de le bac à sable. Il a joué avec la dînette, et avec Nino. La pomme rouge reste dans le panier, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5686,7 +6043,15 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué.
+copain|On a joué.
+papa|Le corps n'est pas une blague.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|Amir a vécu le rouge, près de le bac à sable.
+narrateur|Il a joué avec la dînette, et avec Nino.
+narrateur|La pomme rouge reste dans le panier, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5714,7 +6079,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Près de bleu. Sami pose la dînette. le bac à sable est derrière. On dit merci. Sami prend la main de papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Le bleu s'installe, tout calme. Le ciel est bleu, tout haut. Une pelle bleue repose dans l'herbe. Tu vois le bleu, Amir ? Oui, maman. Amir a encore la dînette, près de le bac à sable. Nino est encore là, tout près. La petite tasse bleue tremble près du bac. On joue encore ? Oui. Oui. Le corps n'est pas une blague. On joue ensemble. On ne commente pas le corps. Merci, Nino. Merci, Amir. Bravo. C'est du bon travail. Amir range la dînette, tout doux. Tu as fini de ranger un peu ? Oui, papa.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5854,7 +6219,27 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Près de bleu. Sami pose la dînette. le bac à sable est derrière. On dit merci. Sami prend la main de papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>narrateur|Le bleu s'installe, tout calme.
+narrateur|Le ciel est bleu, tout haut.
+narrateur|Une pelle bleue repose dans l'herbe.
+maman|Tu vois le bleu, Amir ?
+enfant-m|Oui, maman.
+narrateur|Amir a encore la dînette, près de le bac à sable.
+narrateur|Nino est encore là, tout près.
+narrateur|La petite tasse bleue tremble près du bac.
+papa|On joue encore ?
+enfant-m|Oui.
+copain|Oui.
+maman|Le corps n'est pas une blague.
+maman|On joue ensemble.
+papa|On ne commente pas le corps.
+enfant-m|Merci, Nino.
+copain|Merci, Amir.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Amir range la dînette, tout doux.
+papa|Tu as fini de ranger un peu ?
+enfant-m|Oui, papa.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5882,7 +6267,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Amir a vécu le bleu, près de le bac à sable. Il a joué avec la dînette, et avec Nino. La pelle bleue sèche dans l'herbe, tout sage. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6022,7 +6407,15 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué.
+copain|On a joué.
+papa|Le corps n'est pas une blague.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|Amir a vécu le bleu, près de le bac à sable.
+narrateur|Il a joué avec la dînette, et avec Nino.
+narrateur|La pelle bleue sèche dans l'herbe, tout sage.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6050,7 +6443,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Sami montre vert. Papa a vu le bac à sable. Et la dînette. Un ballon s'immobilise. Sami enfile ses chaussons. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Le vert est partout, tout doux. L'herbe est verte, encore un peu mouillée. Une feuille verte colle à la chaussette. Tu vois le vert, Amir ? Oui, papa. Amir a encore la dînette, près de le bac à sable. Nino est encore là, tout près. Un brin d'herbe verte reste dans la casserole. On joue encore ? Oui. Oui. Le corps n'est pas une blague. On joue ensemble. On ne commente pas le corps. Merci, Nino. Merci, Amir. Bravo. C'est du bon travail. Amir range la dînette, tout doux. Tu as fini de ranger un peu ? Oui, papa.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6190,10 +6583,34 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Sami montre vert. Papa a vu le bac à sable. Et la dînette. Un ballon s'immobilise. Sami enfile ses chaussons. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr"/>
+          <t>narrateur|Le vert est partout, tout doux.
+narrateur|L'herbe est verte, encore un peu mouillée.
+narrateur|Une feuille verte colle à la chaussette.
+papa|Tu vois le vert, Amir ?
+enfant-m|Oui, papa.
+narrateur|Amir a encore la dînette, près de le bac à sable.
+narrateur|Nino est encore là, tout près.
+narrateur|Un brin d'herbe verte reste dans la casserole.
+papa|On joue encore ?
+enfant-m|Oui.
+copain|Oui.
+maman|Le corps n'est pas une blague.
+maman|On joue ensemble.
+papa|On ne commente pas le corps.
+enfant-m|Merci, Nino.
+copain|Merci, Amir.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Amir range la dînette, tout doux.
+papa|Tu as fini de ranger un peu ?
+enfant-m|Oui, papa.</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>feuille</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6218,7 +6635,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Amir a vécu le vert, près de le bac à sable. Il a joué avec la dînette, et avec Nino. La feuille verte ne bouge plus, sur le pull. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6358,7 +6775,15 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué.
+copain|On a joué.
+papa|Le corps n'est pas une blague.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|Amir a vécu le vert, près de le bac à sable.
+narrateur|Il a joué avec la dînette, et avec Nino.
+narrateur|La feuille verte ne bouge plus, sur le pull.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6386,7 +6811,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Sami va vers le toboggan. Un copain plus mince attend. Sami s'assoit à côté. Le corps n'est pas une blague. On joue ensemble. Ils glissent, chacun son tour. Je suis là. On peut jouer ensemble.</t>
+          <t>Amir pose la main sur le toboggan. Le métal est un peu froid. Une marche sonne, tout creux. Nino attend en bas, tout sage. Nino a un corps plus mince. Amir s'assoit à côté, un moment. On joue, chacun son tour. Le corps n'est pas une blague. Tu glisses ? Oui. Nino glisse, tout doux. Puis Amir glisse, tout doux. Bravo. Vous avez attendu. On joue ensemble. On ne commente pas le corps. Encore ? Encore. Le métal reste froid sous les mains. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6526,8 +6951,26 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Sami va vers le toboggan. Un copain plus mince attend. Sami s'assoit à côté. Le corps n'est pas une blague. On joue ensemble. Ils glissent, chacun son tour.
-papa|Je suis là. On peut jouer ensemble.</t>
+          <t>narrateur|Amir pose la main sur le toboggan.
+narrateur|Le métal est un peu froid.
+narrateur|Une marche sonne, tout creux.
+narrateur|Nino attend en bas, tout sage.
+narrateur|Nino a un corps plus mince.
+narrateur|Amir s'assoit à côté, un moment.
+papa|On joue, chacun son tour.
+papa|Le corps n'est pas une blague.
+enfant-m|Tu glisses ?
+copain|Oui.
+narrateur|Nino glisse, tout doux.
+narrateur|Puis Amir glisse, tout doux.
+maman|Bravo.
+maman|Vous avez attendu.
+papa|On joue ensemble.
+papa|On ne commente pas le corps.
+enfant-m|Encore ?
+copain|Encore.
+narrateur|Le métal reste froid sous les mains.
+maman|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr"/>
@@ -6555,7 +6998,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>On joue, sans blague sur le corps ?</t>
+          <t>Ils ont glissé, chacun son tour. On joue ensemble ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6715,7 +7158,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|On joue, sans blague sur le corps ?</t>
+          <t>narrateur|Ils ont glissé, chacun son tour.
+maman|On joue ensemble ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6743,7 +7187,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. On joue. Le corps n'est pas une blague. Sami retient le geste. Papa sourit. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Oui. On joue. Le corps n'est pas une blague. Amir essuie ses mains sur son pull. Le tissu est un peu rêche. Chacun son tour. Bravo. Vous avez attendu. Le métal du toboggan reste froid, tout calme.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6887,7 +7331,15 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On joue. Le corps n'est pas une blague. Sami retient le geste. Papa sourit. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+          <t>maman|Oui.
+maman|On joue.
+maman|Le corps n'est pas une blague.
+narrateur|Amir essuie ses mains sur son pull.
+narrateur|Le tissu est un peu rêche.
+enfant-m|Chacun son tour.
+papa|Bravo.
+papa|Vous avez attendu.
+narrateur|Le métal du toboggan reste froid, tout calme.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6915,7 +7367,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Trois jeux attendent, tout proches. Les cubes, le livre, ou la dînette ? On joue. Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7079,7 +7531,10 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Trois jeux attendent, tout proches.
+maman|Les cubes, le livre, ou la dînette ?
+papa|On joue.
+papa|Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7107,7 +7562,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Sami construit une tour de cubes au pied du toboggan. On joue. Personne ne commente le corps. Je suis là. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Amir prend les cubes en bois. Un cube rouge sent le pin. Un cube vert fait clic. Nino pose un cube, tout droit. Vous construisez ensemble ? Oui. Oui. Le corps n'est pas une blague. On joue. Nino tient la base. Amir pose le petit cube. La tour tient. Elle est haute. Encore un. Bravo. Vous jouez ensemble. Un cube tapote la première marche, tout doux. On est encore près de le toboggan. On joue ensemble. Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7247,12 +7702,33 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Sami construit une tour de cubes au pied du toboggan. On joue. Personne ne commente le corps.
-papa|Je suis là.
-narrateur|Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>narrateur|Amir prend les cubes en bois.
+narrateur|Un cube rouge sent le pin.
+narrateur|Un cube vert fait clic.
+narrateur|Nino pose un cube, tout droit.
+papa|Vous construisez ensemble ?
+enfant-m|Oui.
+copain|Oui.
+maman|Le corps n'est pas une blague.
+maman|On joue.
+papa|Nino tient la base.
+papa|Amir pose le petit cube.
+narrateur|La tour tient.
+enfant-m|Elle est haute.
+copain|Encore un.
+maman|Bravo.
+maman|Vous jouez ensemble.
+narrateur|Un cube tapote la première marche, tout doux.
+narrateur|On est encore près de le toboggan.
+papa|On joue ensemble.
+maman|Le corps n'est pas une blague.</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>cubes</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7277,7 +7753,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>Quelle couleur, maintenant ? Rouge, bleu, ou vert ? On joue encore ensemble.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7445,7 +7921,9 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|Quelle couleur, maintenant ?
+papa|Rouge, bleu, ou vert ?
+maman|On joue encore ensemble.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7473,7 +7951,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi le toboggan. Puis les cubes. Puis rouge. Un vélo passe au loin. Sami plie un pull. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Le rouge arrive, tout vif. Une pomme rouge brille dans l'herbe. Un seau rouge attend, tout près. Tu vois le rouge, Amir ? Oui, papa. Amir a encore les cubes, près de le toboggan. Nino est encore là, tout près. Un cube rouge tapote la rampe, tout petit. On joue encore ? Oui. Oui. Le corps n'est pas une blague. On joue ensemble. On ne commente pas le corps. Merci, Nino. Merci, Amir. Bravo. C'est du bon travail. Amir range les cubes, tout doux. Tu as fini de ranger un peu ? Oui, papa.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7613,10 +8091,34 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi le toboggan. Puis les cubes. Puis rouge. Un vélo passe au loin. Sami plie un pull. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr"/>
+          <t>narrateur|Le rouge arrive, tout vif.
+narrateur|Une pomme rouge brille dans l'herbe.
+narrateur|Un seau rouge attend, tout près.
+papa|Tu vois le rouge, Amir ?
+enfant-m|Oui, papa.
+narrateur|Amir a encore les cubes, près de le toboggan.
+narrateur|Nino est encore là, tout près.
+narrateur|Un cube rouge tapote la rampe, tout petit.
+papa|On joue encore ?
+enfant-m|Oui.
+copain|Oui.
+maman|Le corps n'est pas une blague.
+maman|On joue ensemble.
+papa|On ne commente pas le corps.
+enfant-m|Merci, Nino.
+copain|Merci, Amir.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Amir range les cubes, tout doux.
+papa|Tu as fini de ranger un peu ?
+enfant-m|Oui, papa.</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7641,7 +8143,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Amir a vécu le rouge, près de le toboggan. Il a joué avec les cubes, et avec Nino. La pomme rouge reste dans le panier, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7781,7 +8283,15 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué.
+copain|On a joué.
+papa|Le corps n'est pas une blague.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|Amir a vécu le rouge, près de le toboggan.
+narrateur|Il a joué avec les cubes, et avec Nino.
+narrateur|La pomme rouge reste dans le panier, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7809,7 +8319,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Sami s'arrête près de bleu. les cubes est rangé. On range un objet. Sami boit une gorgée d'eau. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Le bleu s'installe, tout calme. Le ciel est bleu, tout haut. Une pelle bleue repose dans l'herbe. Tu vois le bleu, Amir ? Oui, maman. Amir a encore les cubes, près de le toboggan. Nino est encore là, tout près. L'ombre bleue du toboggan couvre deux cubes. On joue encore ? Oui. Oui. Le corps n'est pas une blague. On joue ensemble. On ne commente pas le corps. Merci, Nino. Merci, Amir. Bravo. C'est du bon travail. Amir range les cubes, tout doux. Tu as fini de ranger un peu ? Oui, papa.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7949,7 +8459,27 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Sami s'arrête près de bleu. les cubes est rangé. On range un objet. Sami boit une gorgée d'eau. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>narrateur|Le bleu s'installe, tout calme.
+narrateur|Le ciel est bleu, tout haut.
+narrateur|Une pelle bleue repose dans l'herbe.
+maman|Tu vois le bleu, Amir ?
+enfant-m|Oui, maman.
+narrateur|Amir a encore les cubes, près de le toboggan.
+narrateur|Nino est encore là, tout près.
+narrateur|L'ombre bleue du toboggan couvre deux cubes.
+papa|On joue encore ?
+enfant-m|Oui.
+copain|Oui.
+maman|Le corps n'est pas une blague.
+maman|On joue ensemble.
+papa|On ne commente pas le corps.
+enfant-m|Merci, Nino.
+copain|Merci, Amir.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Amir range les cubes, tout doux.
+papa|Tu as fini de ranger un peu ?
+enfant-m|Oui, papa.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7977,7 +8507,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Amir a vécu le bleu, près de le toboggan. Il a joué avec les cubes, et avec Nino. La pelle bleue sèche dans l'herbe, tout sage. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8117,7 +8647,15 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué.
+copain|On a joué.
+papa|Le corps n'est pas une blague.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|Amir a vécu le bleu, près de le toboggan.
+narrateur|Il a joué avec les cubes, et avec Nino.
+narrateur|La pelle bleue sèche dans l'herbe, tout sage.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8145,7 +8683,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Sami se souvient de le toboggan. Et de les cubes. Et de vert. Un panier est posé sur le banc. Sami range la tasse. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Le vert est partout, tout doux. L'herbe est verte, encore un peu mouillée. Une feuille verte colle à la chaussette. Tu vois le vert, Amir ? Oui, papa. Amir a encore les cubes, près de le toboggan. Nino est encore là, tout près. Un cube vert attend en bas, dans l'herbe. On joue encore ? Oui. Oui. Le corps n'est pas une blague. On joue ensemble. On ne commente pas le corps. Merci, Nino. Merci, Amir. Bravo. C'est du bon travail. Amir range les cubes, tout doux. Tu as fini de ranger un peu ? Oui, papa.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8285,10 +8823,34 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Sami se souvient de le toboggan. Et de les cubes. Et de vert. Un panier est posé sur le banc. Sami range la tasse. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr"/>
+          <t>narrateur|Le vert est partout, tout doux.
+narrateur|L'herbe est verte, encore un peu mouillée.
+narrateur|Une feuille verte colle à la chaussette.
+papa|Tu vois le vert, Amir ?
+enfant-m|Oui, papa.
+narrateur|Amir a encore les cubes, près de le toboggan.
+narrateur|Nino est encore là, tout près.
+narrateur|Un cube vert attend en bas, dans l'herbe.
+papa|On joue encore ?
+enfant-m|Oui.
+copain|Oui.
+maman|Le corps n'est pas une blague.
+maman|On joue ensemble.
+papa|On ne commente pas le corps.
+enfant-m|Merci, Nino.
+copain|Merci, Amir.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Amir range les cubes, tout doux.
+papa|Tu as fini de ranger un peu ?
+enfant-m|Oui, papa.</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>feuille</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8313,7 +8875,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Amir a vécu le vert, près de le toboggan. Il a joué avec les cubes, et avec Nino. La feuille verte ne bouge plus, sur le pull. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8453,7 +9015,15 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué.
+copain|On a joué.
+papa|Le corps n'est pas une blague.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|Amir a vécu le vert, près de le toboggan.
+narrateur|Il a joué avec les cubes, et avec Nino.
+narrateur|La feuille verte ne bouge plus, sur le pull.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8481,7 +9051,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Sami lit une page avant de glisser. Un copain attend. On joue. Le corps n'est pas une blague. Papa reste tout près. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Amir ouvre le livre. La page sent le papier, un peu sec. Une pomme est dessinée, toute rouge. Nino montre la pomme du doigt. On lit ensemble ? Oui. La pomme. On joue. Le corps n'est pas une blague. L'amitié ne dépend pas de la forme. Amir tourne la page, tout doux. Une feuille collée sert de marque-page. Encore. Bravo, Amir. Tu as partagé le livre. Le livre s'ouvre au pied du toboggan. On est encore près de le toboggan. On joue ensemble. Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8621,10 +9191,32 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Sami lit une page avant de glisser. Un copain attend. On joue. Le corps n'est pas une blague. Papa reste tout près. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr"/>
+          <t>narrateur|Amir ouvre le livre.
+narrateur|La page sent le papier, un peu sec.
+narrateur|Une pomme est dessinée, toute rouge.
+narrateur|Nino montre la pomme du doigt.
+papa|On lit ensemble ?
+enfant-m|Oui.
+copain|La pomme.
+maman|On joue.
+maman|Le corps n'est pas une blague.
+papa|L'amitié ne dépend pas de la forme.
+narrateur|Amir tourne la page, tout doux.
+narrateur|Une feuille collée sert de marque-page.
+enfant-m|Encore.
+maman|Bravo, Amir.
+maman|Tu as partagé le livre.
+narrateur|Le livre s'ouvre au pied du toboggan.
+narrateur|On est encore près de le toboggan.
+papa|On joue ensemble.
+maman|Le corps n'est pas une blague.</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8649,7 +9241,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>Quelle couleur, maintenant ? Rouge, bleu, ou vert ? On joue encore ensemble.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8817,7 +9409,9 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|Quelle couleur, maintenant ?
+papa|Rouge, bleu, ou vert ?
+maman|On joue encore ensemble.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8845,7 +9439,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Avec rouge. Après le livre. Près de le toboggan. Sami s'arrête. Il y a des miettes sur la table. Sami range le toboggan dans sa tête, comme un souvenir. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Le rouge arrive, tout vif. Une pomme rouge brille dans l'herbe. Un seau rouge attend, tout près. Tu vois le rouge, Amir ? Oui, papa. Amir a encore le livre, près de le toboggan. Nino est encore là, tout près. La page rouge se plie un peu, près du métal. On joue encore ? Oui. Oui. Le corps n'est pas une blague. On joue ensemble. On ne commente pas le corps. Merci, Nino. Merci, Amir. Bravo. C'est du bon travail. Amir range le livre, tout doux. Tu as fini de ranger un peu ? Oui, papa.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8985,10 +9579,34 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Avec rouge. Après le livre. Près de le toboggan. Sami s'arrête. Il y a des miettes sur la table. Sami range le toboggan dans sa tête, comme un souvenir. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr"/>
+          <t>narrateur|Le rouge arrive, tout vif.
+narrateur|Une pomme rouge brille dans l'herbe.
+narrateur|Un seau rouge attend, tout près.
+papa|Tu vois le rouge, Amir ?
+enfant-m|Oui, papa.
+narrateur|Amir a encore le livre, près de le toboggan.
+narrateur|Nino est encore là, tout près.
+narrateur|La page rouge se plie un peu, près du métal.
+papa|On joue encore ?
+enfant-m|Oui.
+copain|Oui.
+maman|Le corps n'est pas une blague.
+maman|On joue ensemble.
+papa|On ne commente pas le corps.
+enfant-m|Merci, Nino.
+copain|Merci, Amir.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Amir range le livre, tout doux.
+papa|Tu as fini de ranger un peu ?
+enfant-m|Oui, papa.</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9013,7 +9631,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Amir a vécu le rouge, près de le toboggan. Il a joué avec le livre, et avec Nino. La pomme rouge reste dans le panier, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9153,7 +9771,15 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué.
+copain|On a joué.
+papa|Le corps n'est pas une blague.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|Amir a vécu le rouge, près de le toboggan.
+narrateur|Il a joué avec le livre, et avec Nino.
+narrateur|La pomme rouge reste dans le panier, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9181,7 +9807,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Sami range le livre. bleu reste près de le toboggan. Une pomme brille un peu. Sami serre la main de papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Le bleu s'installe, tout calme. Le ciel est bleu, tout haut. Une pelle bleue repose dans l'herbe. Tu vois le bleu, Amir ? Oui, maman. Amir a encore le livre, près de le toboggan. Nino est encore là, tout près. Le ciel bleu se reflète sur la page lisse. On joue encore ? Oui. Oui. Le corps n'est pas une blague. On joue ensemble. On ne commente pas le corps. Merci, Nino. Merci, Amir. Bravo. C'est du bon travail. Amir range le livre, tout doux. Tu as fini de ranger un peu ? Oui, papa.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9321,7 +9947,27 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Sami range le livre. bleu reste près de le toboggan. Une pomme brille un peu. Sami serre la main de papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>narrateur|Le bleu s'installe, tout calme.
+narrateur|Le ciel est bleu, tout haut.
+narrateur|Une pelle bleue repose dans l'herbe.
+maman|Tu vois le bleu, Amir ?
+enfant-m|Oui, maman.
+narrateur|Amir a encore le livre, près de le toboggan.
+narrateur|Nino est encore là, tout près.
+narrateur|Le ciel bleu se reflète sur la page lisse.
+papa|On joue encore ?
+enfant-m|Oui.
+copain|Oui.
+maman|Le corps n'est pas une blague.
+maman|On joue ensemble.
+papa|On ne commente pas le corps.
+enfant-m|Merci, Nino.
+copain|Merci, Amir.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Amir range le livre, tout doux.
+papa|Tu as fini de ranger un peu ?
+enfant-m|Oui, papa.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9349,7 +9995,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Amir a vécu le bleu, près de le toboggan. Il a joué avec le livre, et avec Nino. La pelle bleue sèche dans l'herbe, tout sage. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9489,7 +10135,15 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué.
+copain|On a joué.
+papa|Le corps n'est pas une blague.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|Amir a vécu le bleu, près de le toboggan.
+narrateur|Il a joué avec le livre, et avec Nino.
+narrateur|La pelle bleue sèche dans l'herbe, tout sage.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9517,7 +10171,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Vert est là. le livre aussi. le toboggan reste dans le souvenir. On entend un oiseau. Sami raccroche un linge. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Le vert est partout, tout doux. L'herbe est verte, encore un peu mouillée. Une feuille verte colle à la chaussette. Tu vois le vert, Amir ? Oui, papa. Amir a encore le livre, près de le toboggan. Nino est encore là, tout près. Une feuille verte sert de marque-page, encore. On joue encore ? Oui. Oui. Le corps n'est pas une blague. On joue ensemble. On ne commente pas le corps. Merci, Nino. Merci, Amir. Bravo. C'est du bon travail. Amir range le livre, tout doux. Tu as fini de ranger un peu ? Oui, papa.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9657,10 +10311,34 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Vert est là. le livre aussi. le toboggan reste dans le souvenir. On entend un oiseau. Sami raccroche un linge. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr"/>
+          <t>narrateur|Le vert est partout, tout doux.
+narrateur|L'herbe est verte, encore un peu mouillée.
+narrateur|Une feuille verte colle à la chaussette.
+papa|Tu vois le vert, Amir ?
+enfant-m|Oui, papa.
+narrateur|Amir a encore le livre, près de le toboggan.
+narrateur|Nino est encore là, tout près.
+narrateur|Une feuille verte sert de marque-page, encore.
+papa|On joue encore ?
+enfant-m|Oui.
+copain|Oui.
+maman|Le corps n'est pas une blague.
+maman|On joue ensemble.
+papa|On ne commente pas le corps.
+enfant-m|Merci, Nino.
+copain|Merci, Amir.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Amir range le livre, tout doux.
+papa|Tu as fini de ranger un peu ?
+enfant-m|Oui, papa.</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>feuille</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9685,7 +10363,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Amir a vécu le vert, près de le toboggan. Il a joué avec le livre, et avec Nino. La feuille verte ne bouge plus, sur le pull. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9825,7 +10503,15 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué.
+copain|On a joué.
+papa|Le corps n'est pas une blague.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|Amir a vécu le vert, près de le toboggan.
+narrateur|Il a joué avec le livre, et avec Nino.
+narrateur|La feuille verte ne bouge plus, sur le pull.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9853,7 +10539,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Sami pose une tasse de dînette sur la marche. On joue. Le corps n'est pas une blague. Papa montre le geste, lentement. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Amir sort la dînette. Une petite assiette sonne, tout creux. Une cuillère miniature est encore tiède. Nino sert le sable, tout doux. Tu sers Nino ? Oui. Merci. On joue ensemble. Le corps n'est pas une blague. Ils posent deux tasses, côte à côte. C'est du goûter. Bravo. Vous avez partagé. On ne commente pas le corps. Une goutte perle au bord de l'assiette. La petite tasse sonne contre le métal. On est encore près de le toboggan. On joue ensemble. Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9993,10 +10679,32 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Sami pose une tasse de dînette sur la marche. On joue. Le corps n'est pas une blague. Papa montre le geste, lentement. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr"/>
+          <t>narrateur|Amir sort la dînette.
+narrateur|Une petite assiette sonne, tout creux.
+narrateur|Une cuillère miniature est encore tiède.
+narrateur|Nino sert le sable, tout doux.
+maman|Tu sers Nino ?
+enfant-m|Oui.
+copain|Merci.
+papa|On joue ensemble.
+papa|Le corps n'est pas une blague.
+narrateur|Ils posent deux tasses, côte à côte.
+enfant-m|C'est du goûter.
+maman|Bravo.
+maman|Vous avez partagé.
+papa|On ne commente pas le corps.
+narrateur|Une goutte perle au bord de l'assiette.
+narrateur|La petite tasse sonne contre le métal.
+narrateur|On est encore près de le toboggan.
+papa|On joue ensemble.
+maman|Le corps n'est pas une blague.</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>assiette</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10021,7 +10729,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>Quelle couleur, maintenant ? Rouge, bleu, ou vert ? On joue encore ensemble.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10189,7 +10897,9 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|Quelle couleur, maintenant ?
+papa|Rouge, bleu, ou vert ?
+maman|On joue encore ensemble.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10217,7 +10927,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint rouge. la dînette est rangé. le toboggan est fini. On rit un peu. Sami écoute papa encore une fois. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Le rouge arrive, tout vif. Une pomme rouge brille dans l'herbe. Un seau rouge attend, tout près. Tu vois le rouge, Amir ? Oui, papa. Amir a encore la dînette, près de le toboggan. Nino est encore là, tout près. La petite tasse rouge sonne contre une marche. On joue encore ? Oui. Oui. Le corps n'est pas une blague. On joue ensemble. On ne commente pas le corps. Merci, Nino. Merci, Amir. Bravo. C'est du bon travail. Amir range la dînette, tout doux. Tu as fini de ranger un peu ? Oui, papa.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10357,10 +11067,34 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint rouge. la dînette est rangé. le toboggan est fini. On rit un peu. Sami écoute papa encore une fois. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr"/>
+          <t>narrateur|Le rouge arrive, tout vif.
+narrateur|Une pomme rouge brille dans l'herbe.
+narrateur|Un seau rouge attend, tout près.
+papa|Tu vois le rouge, Amir ?
+enfant-m|Oui, papa.
+narrateur|Amir a encore la dînette, près de le toboggan.
+narrateur|Nino est encore là, tout près.
+narrateur|La petite tasse rouge sonne contre une marche.
+papa|On joue encore ?
+enfant-m|Oui.
+copain|Oui.
+maman|Le corps n'est pas une blague.
+maman|On joue ensemble.
+papa|On ne commente pas le corps.
+enfant-m|Merci, Nino.
+copain|Merci, Amir.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Amir range la dînette, tout doux.
+papa|Tu as fini de ranger un peu ?
+enfant-m|Oui, papa.</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10385,7 +11119,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Amir a vécu le rouge, près de le toboggan. Il a joué avec la dînette, et avec Nino. La pomme rouge reste dans le panier, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10525,7 +11259,15 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué.
+copain|On a joué.
+papa|Le corps n'est pas une blague.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|Amir a vécu le rouge, près de le toboggan.
+narrateur|Il a joué avec la dînette, et avec Nino.
+narrateur|La pomme rouge reste dans le panier, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10553,7 +11295,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Près de bleu. Sami pose la dînette. le toboggan est derrière. La couverture est douce. Sami sourit. Papa sourit aussi. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Le bleu s'installe, tout calme. Le ciel est bleu, tout haut. Une pelle bleue repose dans l'herbe. Tu vois le bleu, Amir ? Oui, maman. Amir a encore la dînette, près de le toboggan. Nino est encore là, tout près. La casserole bleue refroidit au pied du toboggan. On joue encore ? Oui. Oui. Le corps n'est pas une blague. On joue ensemble. On ne commente pas le corps. Merci, Nino. Merci, Amir. Bravo. C'est du bon travail. Amir range la dînette, tout doux. Tu as fini de ranger un peu ? Oui, papa.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10693,7 +11435,27 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Près de bleu. Sami pose la dînette. le toboggan est derrière. La couverture est douce. Sami sourit. Papa sourit aussi. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>narrateur|Le bleu s'installe, tout calme.
+narrateur|Le ciel est bleu, tout haut.
+narrateur|Une pelle bleue repose dans l'herbe.
+maman|Tu vois le bleu, Amir ?
+enfant-m|Oui, maman.
+narrateur|Amir a encore la dînette, près de le toboggan.
+narrateur|Nino est encore là, tout près.
+narrateur|La casserole bleue refroidit au pied du toboggan.
+papa|On joue encore ?
+enfant-m|Oui.
+copain|Oui.
+maman|Le corps n'est pas une blague.
+maman|On joue ensemble.
+papa|On ne commente pas le corps.
+enfant-m|Merci, Nino.
+copain|Merci, Amir.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Amir range la dînette, tout doux.
+papa|Tu as fini de ranger un peu ?
+enfant-m|Oui, papa.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10721,7 +11483,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Amir a vécu le bleu, près de le toboggan. Il a joué avec la dînette, et avec Nino. La pelle bleue sèche dans l'herbe, tout sage. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10861,7 +11623,15 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué.
+copain|On a joué.
+papa|Le corps n'est pas une blague.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|Amir a vécu le bleu, près de le toboggan.
+narrateur|Il a joué avec la dînette, et avec Nino.
+narrateur|La pelle bleue sèche dans l'herbe, tout sage.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10889,7 +11659,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Sami montre vert. Papa a vu le toboggan. Et la dînette. On écoute jusqu'au bout. Sami pose la dînette à sa place. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Le vert est partout, tout doux. L'herbe est verte, encore un peu mouillée. Une feuille verte colle à la chaussette. Tu vois le vert, Amir ? Oui, papa. Amir a encore la dînette, près de le toboggan. Nino est encore là, tout près. Un brin vert reste collé à la cuillère. On joue encore ? Oui. Oui. Le corps n'est pas une blague. On joue ensemble. On ne commente pas le corps. Merci, Nino. Merci, Amir. Bravo. C'est du bon travail. Amir range la dînette, tout doux. Tu as fini de ranger un peu ? Oui, papa.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11029,10 +11799,34 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Sami montre vert. Papa a vu le toboggan. Et la dînette. On écoute jusqu'au bout. Sami pose la dînette à sa place. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr"/>
+          <t>narrateur|Le vert est partout, tout doux.
+narrateur|L'herbe est verte, encore un peu mouillée.
+narrateur|Une feuille verte colle à la chaussette.
+papa|Tu vois le vert, Amir ?
+enfant-m|Oui, papa.
+narrateur|Amir a encore la dînette, près de le toboggan.
+narrateur|Nino est encore là, tout près.
+narrateur|Un brin vert reste collé à la cuillère.
+papa|On joue encore ?
+enfant-m|Oui.
+copain|Oui.
+maman|Le corps n'est pas une blague.
+maman|On joue ensemble.
+papa|On ne commente pas le corps.
+enfant-m|Merci, Nino.
+copain|Merci, Amir.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Amir range la dînette, tout doux.
+papa|Tu as fini de ranger un peu ?
+enfant-m|Oui, papa.</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>feuille</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11057,7 +11851,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Amir a vécu le vert, près de le toboggan. Il a joué avec la dînette, et avec Nino. La feuille verte ne bouge plus, sur le pull. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11197,7 +11991,15 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué.
+copain|On a joué.
+papa|Le corps n'est pas une blague.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|Amir a vécu le vert, près de le toboggan.
+narrateur|Il a joué avec la dînette, et avec Nino.
+narrateur|La feuille verte ne bouge plus, sur le pull.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11225,7 +12027,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Sami va vers les balançoires. Une feuille tombe du pommier. Un copain d'une autre forme pousse tout doux. Sami joue avec lui. Le corps n'est pas une blague. Papa sourit. On peut jouer ensemble.</t>
+          <t>Amir s'assoit sur la balançoire. La chaîne est froide, un peu rêche. Elle fait un tout petit criiiii. Une feuille tombe du pommier. Nino pousse tout doux, tout près. Nino a une autre forme, tout simplement. On joue ensemble. Le corps n'est pas une blague. Merci, Nino. À moi ? Oui. Chacun son tour. Ils échangent la place, tout calme. L'herbe sent encore la rosée. Bravo, Amir. Tu as joué avec Nino. L'amitié ne dépend pas de la forme. On joue. On joue. La chaîne s'arrête, tout doucement.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11365,7 +12167,26 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Sami va vers les balançoires. Une feuille tombe du pommier. Un copain d'une autre forme pousse tout doux. Sami joue avec lui. Le corps n'est pas une blague. Papa sourit. On peut jouer ensemble.</t>
+          <t>narrateur|Amir s'assoit sur la balançoire.
+narrateur|La chaîne est froide, un peu rêche.
+narrateur|Elle fait un tout petit criiiii.
+narrateur|Une feuille tombe du pommier.
+narrateur|Nino pousse tout doux, tout près.
+narrateur|Nino a une autre forme, tout simplement.
+papa|On joue ensemble.
+papa|Le corps n'est pas une blague.
+enfant-m|Merci, Nino.
+copain|À moi ?
+maman|Oui.
+maman|Chacun son tour.
+narrateur|Ils échangent la place, tout calme.
+narrateur|L'herbe sent encore la rosée.
+papa|Bravo, Amir.
+papa|Tu as joué avec Nino.
+maman|L'amitié ne dépend pas de la forme.
+enfant-m|On joue.
+copain|On joue.
+narrateur|La chaîne s'arrête, tout doucement.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr"/>
@@ -11393,7 +12214,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>On fait quoi ? On joue.</t>
+          <t>Amir a joué avec Nino. On joue ensemble ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11549,7 +12370,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|On fait quoi ? On joue.</t>
+          <t>narrateur|Amir a joué avec Nino.
+papa|On joue ensemble ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11577,7 +12399,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. On joue. Le corps n'est pas une blague. Sami hoche la tête. On continue, avec papa. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Oui. On joue ensemble. Le corps n'est pas une blague. Amir hoche la tête. La chaîne ne crie plus. On joue. Bravo. C'est du bon travail. La feuille reste dans l'herbe, toute plate.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11721,7 +12543,15 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On joue. Le corps n'est pas une blague. Sami hoche la tête. On continue, avec papa. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+          <t>papa|Oui.
+papa|On joue ensemble.
+papa|Le corps n'est pas une blague.
+narrateur|Amir hoche la tête.
+narrateur|La chaîne ne crie plus.
+enfant-m|On joue.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|La feuille reste dans l'herbe, toute plate.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11749,7 +12579,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Trois jeux attendent, tout proches. Les cubes, le livre, ou la dînette ? On joue. Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11913,7 +12743,10 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Trois jeux attendent, tout proches.
+maman|Les cubes, le livre, ou la dînette ?
+papa|On joue.
+papa|Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11941,7 +12774,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Sami empile des cubes près des balançoires. Un copain plus rond tient la base. On joue. Papa reste tout près. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Amir prend les cubes en bois. Un cube rouge sent le pin. Un cube vert fait clic. Nino pose un cube, tout droit. Vous construisez ensemble ? Oui. Oui. Le corps n'est pas une blague. On joue. Nino tient la base. Amir pose le petit cube. La tour tient. Elle est haute. Encore un. Bravo. Vous jouez ensemble. Un cube attend sous la balançoire, tout sage. On est encore près de les balançoires. On joue ensemble. Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12081,10 +12914,33 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Sami empile des cubes près des balançoires. Un copain plus rond tient la base. On joue. Papa reste tout près. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr"/>
+          <t>narrateur|Amir prend les cubes en bois.
+narrateur|Un cube rouge sent le pin.
+narrateur|Un cube vert fait clic.
+narrateur|Nino pose un cube, tout droit.
+papa|Vous construisez ensemble ?
+enfant-m|Oui.
+copain|Oui.
+maman|Le corps n'est pas une blague.
+maman|On joue.
+papa|Nino tient la base.
+papa|Amir pose le petit cube.
+narrateur|La tour tient.
+enfant-m|Elle est haute.
+copain|Encore un.
+maman|Bravo.
+maman|Vous jouez ensemble.
+narrateur|Un cube attend sous la balançoire, tout sage.
+narrateur|On est encore près de les balançoires.
+papa|On joue ensemble.
+maman|Le corps n'est pas une blague.</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>cubes</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12109,7 +12965,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>Quelle couleur, maintenant ? Rouge, bleu, ou vert ? On joue encore ensemble.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12277,7 +13133,9 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|Quelle couleur, maintenant ?
+papa|Rouge, bleu, ou vert ?
+maman|On joue encore ensemble.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12305,7 +13163,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi les balançoires. Puis les cubes. Puis rouge. Une tasse cliquette. Sami essuie ses mains. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Le rouge arrive, tout vif. Une pomme rouge brille dans l'herbe. Un seau rouge attend, tout près. Tu vois le rouge, Amir ? Oui, papa. Amir a encore les cubes, près de les balançoires. Nino est encore là, tout près. Un cube rouge se balance un peu, sur les genoux. On joue encore ? Oui. Oui. Le corps n'est pas une blague. On joue ensemble. On ne commente pas le corps. Merci, Nino. Merci, Amir. Bravo. C'est du bon travail. Amir range les cubes, tout doux. Tu as fini de ranger un peu ? Oui, papa.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12445,10 +13303,34 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi les balançoires. Puis les cubes. Puis rouge. Une tasse cliquette. Sami essuie ses mains. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr"/>
+          <t>narrateur|Le rouge arrive, tout vif.
+narrateur|Une pomme rouge brille dans l'herbe.
+narrateur|Un seau rouge attend, tout près.
+papa|Tu vois le rouge, Amir ?
+enfant-m|Oui, papa.
+narrateur|Amir a encore les cubes, près de les balançoires.
+narrateur|Nino est encore là, tout près.
+narrateur|Un cube rouge se balance un peu, sur les genoux.
+papa|On joue encore ?
+enfant-m|Oui.
+copain|Oui.
+maman|Le corps n'est pas une blague.
+maman|On joue ensemble.
+papa|On ne commente pas le corps.
+enfant-m|Merci, Nino.
+copain|Merci, Amir.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Amir range les cubes, tout doux.
+papa|Tu as fini de ranger un peu ?
+enfant-m|Oui, papa.</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12473,7 +13355,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Amir a vécu le rouge, près de les balançoires. Il a joué avec les cubes, et avec Nino. La pomme rouge reste dans le panier, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12613,7 +13495,15 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué.
+copain|On a joué.
+papa|Le corps n'est pas une blague.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|Amir a vécu le rouge, près de les balançoires.
+narrateur|Il a joué avec les cubes, et avec Nino.
+narrateur|La pomme rouge reste dans le panier, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12641,7 +13531,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Sami s'arrête près de bleu. les cubes est rangé. Le sol est un peu froid. J'ai appris. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Le bleu s'installe, tout calme. Le ciel est bleu, tout haut. Une pelle bleue repose dans l'herbe. Tu vois le bleu, Amir ? Oui, maman. Amir a encore les cubes, près de les balançoires. Nino est encore là, tout près. Un cube bleu attend sous la chaîne froide. On joue encore ? Oui. Oui. Le corps n'est pas une blague. On joue ensemble. On ne commente pas le corps. Merci, Nino. Merci, Amir. Bravo. C'est du bon travail. Amir range les cubes, tout doux. Tu as fini de ranger un peu ? Oui, papa.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12781,9 +13671,27 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Sami s'arrête près de bleu. les cubes est rangé. Le sol est un peu froid.
-enfant-m|J'ai appris.
-narrateur|Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>narrateur|Le bleu s'installe, tout calme.
+narrateur|Le ciel est bleu, tout haut.
+narrateur|Une pelle bleue repose dans l'herbe.
+maman|Tu vois le bleu, Amir ?
+enfant-m|Oui, maman.
+narrateur|Amir a encore les cubes, près de les balançoires.
+narrateur|Nino est encore là, tout près.
+narrateur|Un cube bleu attend sous la chaîne froide.
+papa|On joue encore ?
+enfant-m|Oui.
+copain|Oui.
+maman|Le corps n'est pas une blague.
+maman|On joue ensemble.
+papa|On ne commente pas le corps.
+enfant-m|Merci, Nino.
+copain|Merci, Amir.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Amir range les cubes, tout doux.
+papa|Tu as fini de ranger un peu ?
+enfant-m|Oui, papa.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12811,7 +13719,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Amir a vécu le bleu, près de les balançoires. Il a joué avec les cubes, et avec Nino. La pelle bleue sèche dans l'herbe, tout sage. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12951,7 +13859,15 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué.
+copain|On a joué.
+papa|Le corps n'est pas une blague.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|Amir a vécu le bleu, près de les balançoires.
+narrateur|Il a joué avec les cubes, et avec Nino.
+narrateur|La pelle bleue sèche dans l'herbe, tout sage.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12979,7 +13895,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Sami se souvient de les balançoires. Et de les cubes. Et de vert. L'eau coule, tout petit bruit. Sami s'assoit près de papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Le vert est partout, tout doux. L'herbe est verte, encore un peu mouillée. Une feuille verte colle à la chaussette. Tu vois le vert, Amir ? Oui, papa. Amir a encore les cubes, près de les balançoires. Nino est encore là, tout près. L'herbe verte cache un cube, tout petit. On joue encore ? Oui. Oui. Le corps n'est pas une blague. On joue ensemble. On ne commente pas le corps. Merci, Nino. Merci, Amir. Bravo. C'est du bon travail. Amir range les cubes, tout doux. Tu as fini de ranger un peu ? Oui, papa.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13119,10 +14035,34 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Sami se souvient de les balançoires. Et de les cubes. Et de vert. L'eau coule, tout petit bruit. Sami s'assoit près de papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr"/>
+          <t>narrateur|Le vert est partout, tout doux.
+narrateur|L'herbe est verte, encore un peu mouillée.
+narrateur|Une feuille verte colle à la chaussette.
+papa|Tu vois le vert, Amir ?
+enfant-m|Oui, papa.
+narrateur|Amir a encore les cubes, près de les balançoires.
+narrateur|Nino est encore là, tout près.
+narrateur|L'herbe verte cache un cube, tout petit.
+papa|On joue encore ?
+enfant-m|Oui.
+copain|Oui.
+maman|Le corps n'est pas une blague.
+maman|On joue ensemble.
+papa|On ne commente pas le corps.
+enfant-m|Merci, Nino.
+copain|Merci, Amir.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Amir range les cubes, tout doux.
+papa|Tu as fini de ranger un peu ?
+enfant-m|Oui, papa.</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>feuille</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13147,7 +14087,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Amir a vécu le vert, près de les balançoires. Il a joué avec les cubes, et avec Nino. La feuille verte ne bouge plus, sur le pull. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13287,7 +14227,15 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué.
+copain|On a joué.
+papa|Le corps n'est pas une blague.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|Amir a vécu le vert, près de les balançoires.
+narrateur|Il a joué avec les cubes, et avec Nino.
+narrateur|La feuille verte ne bouge plus, sur le pull.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13315,7 +14263,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Sami montre le livre à un copain plus mince. On joue. Le corps n'est pas une blague. Papa montre le geste, lentement. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Amir ouvre le livre. La page sent le papier, un peu sec. Une pomme est dessinée, toute rouge. Nino montre la pomme du doigt. On lit ensemble ? Oui. La pomme. On joue. Le corps n'est pas une blague. L'amitié ne dépend pas de la forme. Amir tourne la page, tout doux. Une feuille collée sert de marque-page. Encore. Bravo, Amir. Tu as partagé le livre. Le livre est ouvert sur l'herbe, près de la chaîne. On est encore près de les balançoires. On joue ensemble. Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13455,10 +14403,32 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Sami montre le livre à un copain plus mince. On joue. Le corps n'est pas une blague. Papa montre le geste, lentement. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr"/>
+          <t>narrateur|Amir ouvre le livre.
+narrateur|La page sent le papier, un peu sec.
+narrateur|Une pomme est dessinée, toute rouge.
+narrateur|Nino montre la pomme du doigt.
+papa|On lit ensemble ?
+enfant-m|Oui.
+copain|La pomme.
+maman|On joue.
+maman|Le corps n'est pas une blague.
+papa|L'amitié ne dépend pas de la forme.
+narrateur|Amir tourne la page, tout doux.
+narrateur|Une feuille collée sert de marque-page.
+enfant-m|Encore.
+maman|Bravo, Amir.
+maman|Tu as partagé le livre.
+narrateur|Le livre est ouvert sur l'herbe, près de la chaîne.
+narrateur|On est encore près de les balançoires.
+papa|On joue ensemble.
+maman|Le corps n'est pas une blague.</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13483,7 +14453,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>Quelle couleur, maintenant ? Rouge, bleu, ou vert ? On joue encore ensemble.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13651,7 +14621,9 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|Quelle couleur, maintenant ?
+papa|Rouge, bleu, ou vert ?
+maman|On joue encore ensemble.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13679,7 +14651,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Avec rouge. Après le livre. Près de les balançoires. Sami s'arrête. Un galet est encore chaud. Sami répète tout bas le geste. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Le rouge arrive, tout vif. Une pomme rouge brille dans l'herbe. Un seau rouge attend, tout près. Tu vois le rouge, Amir ? Oui, papa. Amir a encore le livre, près de les balançoires. Nino est encore là, tout près. La pomme rouge du livre tremble, tout doux. On joue encore ? Oui. Oui. Le corps n'est pas une blague. On joue ensemble. On ne commente pas le corps. Merci, Nino. Merci, Amir. Bravo. C'est du bon travail. Amir range le livre, tout doux. Tu as fini de ranger un peu ? Oui, papa.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13819,10 +14791,34 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Avec rouge. Après le livre. Près de les balançoires. Sami s'arrête. Un galet est encore chaud. Sami répète tout bas le geste. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr"/>
+          <t>narrateur|Le rouge arrive, tout vif.
+narrateur|Une pomme rouge brille dans l'herbe.
+narrateur|Un seau rouge attend, tout près.
+papa|Tu vois le rouge, Amir ?
+enfant-m|Oui, papa.
+narrateur|Amir a encore le livre, près de les balançoires.
+narrateur|Nino est encore là, tout près.
+narrateur|La pomme rouge du livre tremble, tout doux.
+papa|On joue encore ?
+enfant-m|Oui.
+copain|Oui.
+maman|Le corps n'est pas une blague.
+maman|On joue ensemble.
+papa|On ne commente pas le corps.
+enfant-m|Merci, Nino.
+copain|Merci, Amir.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Amir range le livre, tout doux.
+papa|Tu as fini de ranger un peu ?
+enfant-m|Oui, papa.</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13847,7 +14843,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Amir a vécu le rouge, près de les balançoires. Il a joué avec le livre, et avec Nino. La pomme rouge reste dans le panier, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13987,7 +14983,15 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué.
+copain|On a joué.
+papa|Le corps n'est pas une blague.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|Amir a vécu le rouge, près de les balançoires.
+narrateur|Il a joué avec le livre, et avec Nino.
+narrateur|La pomme rouge reste dans le panier, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -14015,7 +15019,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Sami range le livre. bleu reste près de les balançoires. Le savon sent bon. Sami pose sa tête un moment. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Le bleu s'installe, tout calme. Le ciel est bleu, tout haut. Une pelle bleue repose dans l'herbe. Tu vois le bleu, Amir ? Oui, maman. Amir a encore le livre, près de les balançoires. Nino est encore là, tout près. La page bleue claque un peu, dans l'air. On joue encore ? Oui. Oui. Le corps n'est pas une blague. On joue ensemble. On ne commente pas le corps. Merci, Nino. Merci, Amir. Bravo. C'est du bon travail. Amir range le livre, tout doux. Tu as fini de ranger un peu ? Oui, papa.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14155,7 +15159,27 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Sami range le livre. bleu reste près de les balançoires. Le savon sent bon. Sami pose sa tête un moment. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>narrateur|Le bleu s'installe, tout calme.
+narrateur|Le ciel est bleu, tout haut.
+narrateur|Une pelle bleue repose dans l'herbe.
+maman|Tu vois le bleu, Amir ?
+enfant-m|Oui, maman.
+narrateur|Amir a encore le livre, près de les balançoires.
+narrateur|Nino est encore là, tout près.
+narrateur|La page bleue claque un peu, dans l'air.
+papa|On joue encore ?
+enfant-m|Oui.
+copain|Oui.
+maman|Le corps n'est pas une blague.
+maman|On joue ensemble.
+papa|On ne commente pas le corps.
+enfant-m|Merci, Nino.
+copain|Merci, Amir.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Amir range le livre, tout doux.
+papa|Tu as fini de ranger un peu ?
+enfant-m|Oui, papa.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14183,7 +15207,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Amir a vécu le bleu, près de les balançoires. Il a joué avec le livre, et avec Nino. La pelle bleue sèche dans l'herbe, tout sage. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14323,7 +15347,15 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué.
+copain|On a joué.
+papa|Le corps n'est pas une blague.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|Amir a vécu le bleu, près de les balançoires.
+narrateur|Il a joué avec le livre, et avec Nino.
+narrateur|La pelle bleue sèche dans l'herbe, tout sage.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14351,7 +15383,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Vert est là. le livre aussi. les balançoires reste dans le souvenir. Une chaussette est encore sablée. Sami ferme la porte, tout doux. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Le vert est partout, tout doux. L'herbe est verte, encore un peu mouillée. Une feuille verte colle à la chaussette. Tu vois le vert, Amir ? Oui, papa. Amir a encore le livre, près de les balançoires. Nino est encore là, tout près. Une feuille verte s'envole du livre, tout loin. On joue encore ? Oui. Oui. Le corps n'est pas une blague. On joue ensemble. On ne commente pas le corps. Merci, Nino. Merci, Amir. Bravo. C'est du bon travail. Amir range le livre, tout doux. Tu as fini de ranger un peu ? Oui, papa.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14491,10 +15523,34 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Vert est là. le livre aussi. les balançoires reste dans le souvenir. Une chaussette est encore sablée. Sami ferme la porte, tout doux. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr"/>
+          <t>narrateur|Le vert est partout, tout doux.
+narrateur|L'herbe est verte, encore un peu mouillée.
+narrateur|Une feuille verte colle à la chaussette.
+papa|Tu vois le vert, Amir ?
+enfant-m|Oui, papa.
+narrateur|Amir a encore le livre, près de les balançoires.
+narrateur|Nino est encore là, tout près.
+narrateur|Une feuille verte s'envole du livre, tout loin.
+papa|On joue encore ?
+enfant-m|Oui.
+copain|Oui.
+maman|Le corps n'est pas une blague.
+maman|On joue ensemble.
+papa|On ne commente pas le corps.
+enfant-m|Merci, Nino.
+copain|Merci, Amir.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Amir range le livre, tout doux.
+papa|Tu as fini de ranger un peu ?
+enfant-m|Oui, papa.</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>feuille</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14519,7 +15575,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Amir a vécu le vert, près de les balançoires. Il a joué avec le livre, et avec Nino. La feuille verte ne bouge plus, sur le pull. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14659,7 +15715,15 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué.
+copain|On a joué.
+papa|Le corps n'est pas une blague.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|Amir a vécu le vert, près de les balançoires.
+narrateur|Il a joué avec le livre, et avec Nino.
+narrateur|La feuille verte ne bouge plus, sur le pull.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14687,7 +15751,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Sami sert un galet dans la dînette. On joue. Le corps n'est pas une blague. Je suis là. Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Amir sort la dînette. Une petite assiette sonne, tout creux. Une cuillère miniature est encore tiède. Nino sert le sable, tout doux. Tu sers Nino ? Oui. Merci. On joue ensemble. Le corps n'est pas une blague. Ils posent deux tasses, côte à côte. C'est du goûter. Bravo. Vous avez partagé. On ne commente pas le corps. Une goutte perle au bord de l'assiette. La dînette a une place, sur les genoux. On est encore près de les balançoires. On joue ensemble. Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14827,12 +15891,32 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Sami sert un galet dans la dînette. On joue. Le corps n'est pas une blague.
-papa|Je suis là.
-narrateur|Le corps n'est pas une blague. On joue ensemble. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr"/>
+          <t>narrateur|Amir sort la dînette.
+narrateur|Une petite assiette sonne, tout creux.
+narrateur|Une cuillère miniature est encore tiède.
+narrateur|Nino sert le sable, tout doux.
+maman|Tu sers Nino ?
+enfant-m|Oui.
+copain|Merci.
+papa|On joue ensemble.
+papa|Le corps n'est pas une blague.
+narrateur|Ils posent deux tasses, côte à côte.
+enfant-m|C'est du goûter.
+maman|Bravo.
+maman|Vous avez partagé.
+papa|On ne commente pas le corps.
+narrateur|Une goutte perle au bord de l'assiette.
+narrateur|La dînette a une place, sur les genoux.
+narrateur|On est encore près de les balançoires.
+papa|On joue ensemble.
+maman|Le corps n'est pas une blague.</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>assiette</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14857,7 +15941,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>Quelle couleur, maintenant ? Rouge, bleu, ou vert ? On joue encore ensemble.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15025,7 +16109,9 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|Quelle couleur, maintenant ?
+papa|Rouge, bleu, ou vert ?
+maman|On joue encore ensemble.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15053,7 +16139,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint rouge. la dînette est rangé. les balançoires est fini. On attend son tour. Sami souffle, puis sourit à papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Le rouge arrive, tout vif. Une pomme rouge brille dans l'herbe. Un seau rouge attend, tout près. Tu vois le rouge, Amir ? Oui, papa. Amir a encore la dînette, près de les balançoires. Nino est encore là, tout près. La tasse rouge a une place, sur les genoux. On joue encore ? Oui. Oui. Le corps n'est pas une blague. On joue ensemble. On ne commente pas le corps. Merci, Nino. Merci, Amir. Bravo. C'est du bon travail. Amir range la dînette, tout doux. Tu as fini de ranger un peu ? Oui, papa.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15193,10 +16279,34 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint rouge. la dînette est rangé. les balançoires est fini. On attend son tour. Sami souffle, puis sourit à papa. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr"/>
+          <t>narrateur|Le rouge arrive, tout vif.
+narrateur|Une pomme rouge brille dans l'herbe.
+narrateur|Un seau rouge attend, tout près.
+papa|Tu vois le rouge, Amir ?
+enfant-m|Oui, papa.
+narrateur|Amir a encore la dînette, près de les balançoires.
+narrateur|Nino est encore là, tout près.
+narrateur|La tasse rouge a une place, sur les genoux.
+papa|On joue encore ?
+enfant-m|Oui.
+copain|Oui.
+maman|Le corps n'est pas une blague.
+maman|On joue ensemble.
+papa|On ne commente pas le corps.
+enfant-m|Merci, Nino.
+copain|Merci, Amir.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Amir range la dînette, tout doux.
+papa|Tu as fini de ranger un peu ?
+enfant-m|Oui, papa.</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15221,7 +16331,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Amir a vécu le rouge, près de les balançoires. Il a joué avec la dînette, et avec Nino. La pomme rouge reste dans le panier, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15361,7 +16471,15 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué.
+copain|On a joué.
+papa|Le corps n'est pas une blague.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|Amir a vécu le rouge, près de les balançoires.
+narrateur|Il a joué avec la dînette, et avec Nino.
+narrateur|La pomme rouge reste dans le panier, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15389,7 +16507,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Près de bleu. Sami pose la dînette. les balançoires est derrière. Le vent est doux. Sami tend bleu à maman. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Le bleu s'installe, tout calme. Le ciel est bleu, tout haut. Une pelle bleue repose dans l'herbe. Tu vois le bleu, Amir ? Oui, maman. Amir a encore la dînette, près de les balançoires. Nino est encore là, tout près. La petite assiette bleue reflète le ciel. On joue encore ? Oui. Oui. Le corps n'est pas une blague. On joue ensemble. On ne commente pas le corps. Merci, Nino. Merci, Amir. Bravo. C'est du bon travail. Amir range la dînette, tout doux. Tu as fini de ranger un peu ? Oui, papa.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15529,7 +16647,27 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Près de bleu. Sami pose la dînette. les balançoires est derrière. Le vent est doux. Sami tend bleu à maman. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>narrateur|Le bleu s'installe, tout calme.
+narrateur|Le ciel est bleu, tout haut.
+narrateur|Une pelle bleue repose dans l'herbe.
+maman|Tu vois le bleu, Amir ?
+enfant-m|Oui, maman.
+narrateur|Amir a encore la dînette, près de les balançoires.
+narrateur|Nino est encore là, tout près.
+narrateur|La petite assiette bleue reflète le ciel.
+papa|On joue encore ?
+enfant-m|Oui.
+copain|Oui.
+maman|Le corps n'est pas une blague.
+maman|On joue ensemble.
+papa|On ne commente pas le corps.
+enfant-m|Merci, Nino.
+copain|Merci, Amir.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Amir range la dînette, tout doux.
+papa|Tu as fini de ranger un peu ?
+enfant-m|Oui, papa.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15557,7 +16695,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Amir a vécu le bleu, près de les balançoires. Il a joué avec la dînette, et avec Nino. La pelle bleue sèche dans l'herbe, tout sage. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15697,7 +16835,15 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué.
+copain|On a joué.
+papa|Le corps n'est pas une blague.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|Amir a vécu le bleu, près de les balançoires.
+narrateur|Il a joué avec la dînette, et avec Nino.
+narrateur|La pelle bleue sèche dans l'herbe, tout sage.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15725,7 +16871,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Sami montre vert. Papa a vu les balançoires. Et la dînette. Les chaussures font toc toc. Sami chuchote : c'est fini. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
+          <t>Le vert est partout, tout doux. L'herbe est verte, encore un peu mouillée. Une feuille verte colle à la chaussette. Tu vois le vert, Amir ? Oui, papa. Amir a encore la dînette, près de les balançoires. Nino est encore là, tout près. Un brin vert reste au fond de l'assiette. On joue encore ? Oui. Oui. Le corps n'est pas une blague. On joue ensemble. On ne commente pas le corps. Merci, Nino. Merci, Amir. Bravo. C'est du bon travail. Amir range la dînette, tout doux. Tu as fini de ranger un peu ? Oui, papa.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15865,10 +17011,34 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Sami montre vert. Papa a vu les balançoires. Et la dînette. Les chaussures font toc toc. Sami chuchote : c'est fini. Le corps n'est pas une blague. On joue ensemble. On joue. On ne commente pas le corps. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr"/>
+          <t>narrateur|Le vert est partout, tout doux.
+narrateur|L'herbe est verte, encore un peu mouillée.
+narrateur|Une feuille verte colle à la chaussette.
+papa|Tu vois le vert, Amir ?
+enfant-m|Oui, papa.
+narrateur|Amir a encore la dînette, près de les balançoires.
+narrateur|Nino est encore là, tout près.
+narrateur|Un brin vert reste au fond de l'assiette.
+papa|On joue encore ?
+enfant-m|Oui.
+copain|Oui.
+maman|Le corps n'est pas une blague.
+maman|On joue ensemble.
+papa|On ne commente pas le corps.
+enfant-m|Merci, Nino.
+copain|Merci, Amir.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Amir range la dînette, tout doux.
+papa|Tu as fini de ranger un peu ?
+enfant-m|Oui, papa.</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>feuille</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15893,7 +17063,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Amir a vécu le vert, près de les balançoires. Il a joué avec la dînette, et avec Nino. La feuille verte ne bouge plus, sur le pull. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16033,7 +17203,15 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué.
+copain|On a joué.
+papa|Le corps n'est pas une blague.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|Amir a vécu le vert, près de les balançoires.
+narrateur|Il a joué avec la dînette, et avec Nino.
+narrateur|La feuille verte ne bouge plus, sur le pull.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16055,7 +17233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16149,6 +17327,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>
